--- a/dados/excel/composicao_categoria_mes.xlsx
+++ b/dados/excel/composicao_categoria_mes.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$H$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$H$286</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,9 +127,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -139,10 +136,10 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,6 +149,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -640,7 +640,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>﻿ano</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Número decimal (#,##0,00)</t>
+          <t>Número inteiro (#,##0)</t>
         </is>
       </c>
     </row>
@@ -819,14 +819,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H281"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -835,7 +835,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>﻿ano</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -878,26 +878,26 @@
       <c r="A2" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="10" t="n">
         <v>60393496.14</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="11" t="n">
         <v>12945</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="11" t="n">
         <v>8427</v>
       </c>
       <c r="H2" s="12" t="n">
@@ -908,26 +908,26 @@
       <c r="A3" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>4915889.02</v>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F3" s="16" t="n">
         <v>578</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="16" t="n">
         <v>488</v>
       </c>
       <c r="H3" s="17" t="n">
@@ -938,26 +938,26 @@
       <c r="A4" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="10" t="n">
         <v>2822171.55</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="11" t="n">
         <v>2331</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="11" t="n">
         <v>2013</v>
       </c>
       <c r="H4" s="12" t="n">
@@ -968,26 +968,26 @@
       <c r="A5" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="15" t="n">
         <v>1094560.85</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="16" t="n">
         <v>287</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="16" t="n">
         <v>287</v>
       </c>
       <c r="H5" s="17" t="n">
@@ -998,26 +998,26 @@
       <c r="A6" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>1048574.78</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="11" t="n">
         <v>75</v>
       </c>
       <c r="H6" s="12" t="n">
@@ -1028,26 +1028,26 @@
       <c r="A7" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="15" t="n">
         <v>49583618.86</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="16" t="n">
         <v>8703</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="16" t="n">
         <v>8126</v>
       </c>
       <c r="H7" s="17" t="n">
@@ -1058,26 +1058,26 @@
       <c r="A8" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>5873807.24</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="11" t="n">
         <v>693</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="11" t="n">
         <v>558</v>
       </c>
       <c r="H8" s="12" t="n">
@@ -1088,26 +1088,26 @@
       <c r="A9" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="15" t="n">
         <v>1639955.37</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="16" t="n">
         <v>706</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="16" t="n">
         <v>671</v>
       </c>
       <c r="H9" s="17" t="n">
@@ -1118,26 +1118,26 @@
       <c r="A10" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>1206565.65</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="11" t="n">
         <v>104</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="11" t="n">
         <v>88</v>
       </c>
       <c r="H10" s="12" t="n">
@@ -1148,26 +1148,26 @@
       <c r="A11" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="15" t="n">
         <v>1073968.04</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="16" t="n">
         <v>286</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="16" t="n">
         <v>286</v>
       </c>
       <c r="H11" s="17" t="n">
@@ -1178,26 +1178,26 @@
       <c r="A12" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10" t="n">
         <v>57279522.14</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="11" t="n">
         <v>8865</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="11" t="n">
         <v>8128</v>
       </c>
       <c r="H12" s="12" t="n">
@@ -1208,26 +1208,26 @@
       <c r="A13" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="15" t="n">
         <v>6093179.29</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="16" t="n">
         <v>663</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="16" t="n">
         <v>570</v>
       </c>
       <c r="H13" s="17" t="n">
@@ -1238,26 +1238,26 @@
       <c r="A14" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>3234979.61</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="11" t="n">
         <v>2331</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="11" t="n">
         <v>2266</v>
       </c>
       <c r="H14" s="12" t="n">
@@ -1268,26 +1268,26 @@
       <c r="A15" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="15" t="n">
         <v>1191034.08</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="16" t="n">
         <v>95</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="16" t="n">
         <v>90</v>
       </c>
       <c r="H15" s="17" t="n">
@@ -1298,26 +1298,26 @@
       <c r="A16" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="10" t="n">
         <v>1066607.72</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="11" t="n">
         <v>283</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="11" t="n">
         <v>283</v>
       </c>
       <c r="H16" s="12" t="n">
@@ -1328,26 +1328,26 @@
       <c r="A17" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="15" t="n">
         <v>59368991.9</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="16" t="n">
         <v>8774</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="16" t="n">
         <v>8115</v>
       </c>
       <c r="H17" s="17" t="n">
@@ -1358,26 +1358,26 @@
       <c r="A18" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="10" t="n">
         <v>6230179.13</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="11" t="n">
         <v>650</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="11" t="n">
         <v>567</v>
       </c>
       <c r="H18" s="12" t="n">
@@ -1388,26 +1388,26 @@
       <c r="A19" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="15" t="n">
         <v>4361280.49</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="16" t="n">
         <v>2587</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="16" t="n">
         <v>2528</v>
       </c>
       <c r="H19" s="17" t="n">
@@ -1418,26 +1418,26 @@
       <c r="A20" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="10" t="n">
         <v>1334714.75</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="11" t="n">
         <v>98</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="11" t="n">
         <v>91</v>
       </c>
       <c r="H20" s="12" t="n">
@@ -1448,26 +1448,26 @@
       <c r="A21" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="15" t="n">
         <v>1164963.75</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="16" t="n">
         <v>278</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="16" t="n">
         <v>278</v>
       </c>
       <c r="H21" s="17" t="n">
@@ -1478,26 +1478,26 @@
       <c r="A22" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="10" t="n">
         <v>61802124.97</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="11" t="n">
         <v>8786</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="11" t="n">
         <v>8282</v>
       </c>
       <c r="H22" s="12" t="n">
@@ -1508,26 +1508,26 @@
       <c r="A23" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="15" t="n">
         <v>6708090.3</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="16" t="n">
         <v>665</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="16" t="n">
         <v>564</v>
       </c>
       <c r="H23" s="17" t="n">
@@ -1538,26 +1538,26 @@
       <c r="A24" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="10" t="n">
         <v>4244662.25</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="11" t="n">
         <v>2660</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="11" t="n">
         <v>2545</v>
       </c>
       <c r="H24" s="12" t="n">
@@ -1568,26 +1568,26 @@
       <c r="A25" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="15" t="n">
         <v>1281422.71</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="16" t="n">
         <v>89</v>
       </c>
       <c r="H25" s="17" t="n">
@@ -1598,26 +1598,26 @@
       <c r="A26" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="10" t="n">
         <v>1161974.75</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="11" t="n">
         <v>287</v>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="G26" s="11" t="n">
         <v>287</v>
       </c>
       <c r="H26" s="12" t="n">
@@ -1628,26 +1628,26 @@
       <c r="A27" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="15" t="n">
         <v>61873303.02</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="16" t="n">
         <v>9023</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="16" t="n">
         <v>8427</v>
       </c>
       <c r="H27" s="17" t="n">
@@ -1658,26 +1658,26 @@
       <c r="A28" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="10" t="n">
         <v>6390688.81</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="11" t="n">
         <v>619</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="11" t="n">
         <v>553</v>
       </c>
       <c r="H28" s="12" t="n">
@@ -1688,26 +1688,26 @@
       <c r="A29" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="15" t="n">
         <v>4230676.56</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="16" t="n">
         <v>2702</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="16" t="n">
         <v>2569</v>
       </c>
       <c r="H29" s="17" t="n">
@@ -1718,26 +1718,26 @@
       <c r="A30" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="10" t="n">
         <v>1211743.38</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G30" s="11" t="n">
         <v>89</v>
       </c>
       <c r="H30" s="12" t="n">
@@ -1748,26 +1748,26 @@
       <c r="A31" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="15" t="n">
         <v>1152925.4</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="16" t="n">
         <v>277</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="16" t="n">
         <v>277</v>
       </c>
       <c r="H31" s="17" t="n">
@@ -1778,26 +1778,26 @@
       <c r="A32" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="10" t="n">
         <v>63064469.43</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="11" t="n">
         <v>9310</v>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="G32" s="11" t="n">
         <v>8458</v>
       </c>
       <c r="H32" s="12" t="n">
@@ -1808,26 +1808,26 @@
       <c r="A33" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="15" t="n">
         <v>6683616.93</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="16" t="n">
         <v>705</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="16" t="n">
         <v>569</v>
       </c>
       <c r="H33" s="17" t="n">
@@ -1838,26 +1838,26 @@
       <c r="A34" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="10" t="n">
         <v>3656619</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="11" t="n">
         <v>2432</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="11" t="n">
         <v>2401</v>
       </c>
       <c r="H34" s="12" t="n">
@@ -1868,26 +1868,26 @@
       <c r="A35" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="15" t="n">
         <v>1379701.47</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="F35" s="16" t="n">
         <v>109</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="16" t="n">
         <v>89</v>
       </c>
       <c r="H35" s="17" t="n">
@@ -1898,26 +1898,26 @@
       <c r="A36" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="10" t="n">
         <v>1161672.62</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="11" t="n">
         <v>276</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="11" t="n">
         <v>276</v>
       </c>
       <c r="H36" s="12" t="n">
@@ -1928,26 +1928,26 @@
       <c r="A37" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B37" s="14" t="n">
+      <c r="B37" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="15" t="n">
         <v>61096962.61</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="F37" s="16" t="n">
         <v>8858</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="16" t="n">
         <v>8414</v>
       </c>
       <c r="H37" s="17" t="n">
@@ -1958,26 +1958,26 @@
       <c r="A38" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="10" t="n">
         <v>6299861.26</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="11" t="n">
         <v>651</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G38" s="11" t="n">
         <v>567</v>
       </c>
       <c r="H38" s="12" t="n">
@@ -1988,26 +1988,26 @@
       <c r="A39" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B39" s="14" t="n">
+      <c r="B39" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="15" t="n">
         <v>3348849.2</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="F39" s="16" t="n">
         <v>2543</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="16" t="n">
         <v>2493</v>
       </c>
       <c r="H39" s="17" t="n">
@@ -2018,26 +2018,26 @@
       <c r="A40" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="10" t="n">
         <v>1284865.08</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="11" t="n">
         <v>89</v>
       </c>
       <c r="H40" s="12" t="n">
@@ -2048,26 +2048,26 @@
       <c r="A41" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B41" s="14" t="n">
+      <c r="B41" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="15" t="n">
         <v>1091282.17</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F41" s="16" t="n">
         <v>273</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="16" t="n">
         <v>273</v>
       </c>
       <c r="H41" s="17" t="n">
@@ -2078,26 +2078,26 @@
       <c r="A42" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="10" t="n">
         <v>62393869.1</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="11" t="n">
         <v>9453</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="11" t="n">
         <v>8394</v>
       </c>
       <c r="H42" s="12" t="n">
@@ -2108,26 +2108,26 @@
       <c r="A43" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="15" t="n">
         <v>6749389.23</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="F43" s="16" t="n">
         <v>696</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="16" t="n">
         <v>574</v>
       </c>
       <c r="H43" s="17" t="n">
@@ -2138,26 +2138,26 @@
       <c r="A44" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="10" t="n">
         <v>4272257.82</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="11" t="n">
         <v>2718</v>
       </c>
-      <c r="G44" s="8" t="n">
+      <c r="G44" s="11" t="n">
         <v>2699</v>
       </c>
       <c r="H44" s="12" t="n">
@@ -2168,26 +2168,26 @@
       <c r="A45" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="15" t="n">
         <v>1366039.89</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="F45" s="16" t="n">
         <v>102</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="16" t="n">
         <v>89</v>
       </c>
       <c r="H45" s="17" t="n">
@@ -2198,26 +2198,26 @@
       <c r="A46" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="10" t="n">
         <v>1089654.55</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="11" t="n">
         <v>278</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G46" s="11" t="n">
         <v>272</v>
       </c>
       <c r="H46" s="12" t="n">
@@ -2228,26 +2228,26 @@
       <c r="A47" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B47" s="14" t="n">
+      <c r="B47" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="15" t="n">
         <v>65295323.77</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="F47" s="16" t="n">
         <v>10399</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="16" t="n">
         <v>8431</v>
       </c>
       <c r="H47" s="17" t="n">
@@ -2258,26 +2258,26 @@
       <c r="A48" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E48" s="11" t="n">
+      <c r="E48" s="10" t="n">
         <v>6466189.58</v>
       </c>
-      <c r="F48" s="8" t="n">
+      <c r="F48" s="11" t="n">
         <v>650</v>
       </c>
-      <c r="G48" s="8" t="n">
+      <c r="G48" s="11" t="n">
         <v>568</v>
       </c>
       <c r="H48" s="12" t="n">
@@ -2288,26 +2288,26 @@
       <c r="A49" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B49" s="14" t="n">
+      <c r="B49" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="15" t="n">
         <v>4233211.39</v>
       </c>
-      <c r="F49" s="13" t="n">
+      <c r="F49" s="16" t="n">
         <v>2651</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="G49" s="16" t="n">
         <v>2591</v>
       </c>
       <c r="H49" s="17" t="n">
@@ -2318,26 +2318,26 @@
       <c r="A50" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E50" s="11" t="n">
+      <c r="E50" s="10" t="n">
         <v>1243288.63</v>
       </c>
-      <c r="F50" s="8" t="n">
+      <c r="F50" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="G50" s="8" t="n">
+      <c r="G50" s="11" t="n">
         <v>85</v>
       </c>
       <c r="H50" s="12" t="n">
@@ -2348,26 +2348,26 @@
       <c r="A51" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B51" s="14" t="n">
+      <c r="B51" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="15" t="n">
         <v>1227949.42</v>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="F51" s="16" t="n">
         <v>333</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="G51" s="16" t="n">
         <v>270</v>
       </c>
       <c r="H51" s="17" t="n">
@@ -2378,26 +2378,26 @@
       <c r="A52" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B52" s="9" t="n">
+      <c r="B52" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E52" s="11" t="n">
+      <c r="E52" s="10" t="n">
         <v>85753505.28</v>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="F52" s="11" t="n">
         <v>8894</v>
       </c>
-      <c r="G52" s="8" t="n">
+      <c r="G52" s="11" t="n">
         <v>8386</v>
       </c>
       <c r="H52" s="12" t="n">
@@ -2408,26 +2408,26 @@
       <c r="A53" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B53" s="14" t="n">
+      <c r="B53" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="15" t="n">
         <v>9416946.720000001</v>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="F53" s="16" t="n">
         <v>647</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="G53" s="16" t="n">
         <v>567</v>
       </c>
       <c r="H53" s="17" t="n">
@@ -2438,26 +2438,26 @@
       <c r="A54" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E54" s="11" t="n">
+      <c r="E54" s="10" t="n">
         <v>4777866.02</v>
       </c>
-      <c r="F54" s="8" t="n">
+      <c r="F54" s="11" t="n">
         <v>2628</v>
       </c>
-      <c r="G54" s="8" t="n">
+      <c r="G54" s="11" t="n">
         <v>2596</v>
       </c>
       <c r="H54" s="12" t="n">
@@ -2468,26 +2468,26 @@
       <c r="A55" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B55" s="14" t="n">
+      <c r="B55" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C55" s="15" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="15" t="n">
         <v>1674493.67</v>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="F55" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="G55" s="16" t="n">
         <v>82</v>
       </c>
       <c r="H55" s="17" t="n">
@@ -2498,26 +2498,26 @@
       <c r="A56" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B56" s="9" t="n">
+      <c r="B56" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E56" s="11" t="n">
+      <c r="E56" s="10" t="n">
         <v>1652452.77</v>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="F56" s="11" t="n">
         <v>267</v>
       </c>
-      <c r="G56" s="8" t="n">
+      <c r="G56" s="11" t="n">
         <v>267</v>
       </c>
       <c r="H56" s="12" t="n">
@@ -2528,26 +2528,26 @@
       <c r="A57" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B57" s="14" t="n">
+      <c r="B57" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C57" s="15" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E57" s="15" t="n">
         <v>118642421.65</v>
       </c>
-      <c r="F57" s="13" t="n">
+      <c r="F57" s="16" t="n">
         <v>17355</v>
       </c>
-      <c r="G57" s="13" t="n">
+      <c r="G57" s="16" t="n">
         <v>8348</v>
       </c>
       <c r="H57" s="17" t="n">
@@ -2558,26 +2558,26 @@
       <c r="A58" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B58" s="9" t="n">
+      <c r="B58" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E58" s="11" t="n">
+      <c r="E58" s="10" t="n">
         <v>12603196.16</v>
       </c>
-      <c r="F58" s="8" t="n">
+      <c r="F58" s="11" t="n">
         <v>1272</v>
       </c>
-      <c r="G58" s="8" t="n">
+      <c r="G58" s="11" t="n">
         <v>569</v>
       </c>
       <c r="H58" s="12" t="n">
@@ -2588,26 +2588,26 @@
       <c r="A59" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B59" s="14" t="n">
+      <c r="B59" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="E59" s="15" t="n">
         <v>5527676.17</v>
       </c>
-      <c r="F59" s="13" t="n">
+      <c r="F59" s="16" t="n">
         <v>2711</v>
       </c>
-      <c r="G59" s="13" t="n">
+      <c r="G59" s="16" t="n">
         <v>2444</v>
       </c>
       <c r="H59" s="17" t="n">
@@ -2618,26 +2618,26 @@
       <c r="A60" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B60" s="9" t="n">
+      <c r="B60" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E60" s="11" t="n">
+      <c r="E60" s="10" t="n">
         <v>2199443.73</v>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="F60" s="11" t="n">
         <v>511</v>
       </c>
-      <c r="G60" s="8" t="n">
+      <c r="G60" s="11" t="n">
         <v>266</v>
       </c>
       <c r="H60" s="12" t="n">
@@ -2648,26 +2648,26 @@
       <c r="A61" s="13" t="n">
         <v>2022</v>
       </c>
-      <c r="B61" s="14" t="n">
+      <c r="B61" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E61" s="16" t="n">
+      <c r="E61" s="15" t="n">
         <v>2180952.69</v>
       </c>
-      <c r="F61" s="13" t="n">
+      <c r="F61" s="16" t="n">
         <v>179</v>
       </c>
-      <c r="G61" s="13" t="n">
+      <c r="G61" s="16" t="n">
         <v>85</v>
       </c>
       <c r="H61" s="17" t="n">
@@ -2678,26 +2678,26 @@
       <c r="A62" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B62" s="9" t="n">
+      <c r="B62" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E62" s="11" t="n">
+      <c r="E62" s="10" t="n">
         <v>69362430.34</v>
       </c>
-      <c r="F62" s="8" t="n">
+      <c r="F62" s="11" t="n">
         <v>12519</v>
       </c>
-      <c r="G62" s="8" t="n">
+      <c r="G62" s="11" t="n">
         <v>8223</v>
       </c>
       <c r="H62" s="12" t="n">
@@ -2708,26 +2708,26 @@
       <c r="A63" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B63" s="14" t="n">
+      <c r="B63" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E63" s="16" t="n">
+      <c r="E63" s="15" t="n">
         <v>6526385.35</v>
       </c>
-      <c r="F63" s="13" t="n">
+      <c r="F63" s="16" t="n">
         <v>627</v>
       </c>
-      <c r="G63" s="13" t="n">
+      <c r="G63" s="16" t="n">
         <v>565</v>
       </c>
       <c r="H63" s="17" t="n">
@@ -2738,26 +2738,26 @@
       <c r="A64" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B64" s="9" t="n">
+      <c r="B64" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E64" s="11" t="n">
+      <c r="E64" s="10" t="n">
         <v>2951158.34</v>
       </c>
-      <c r="F64" s="8" t="n">
+      <c r="F64" s="11" t="n">
         <v>1964</v>
       </c>
-      <c r="G64" s="8" t="n">
+      <c r="G64" s="11" t="n">
         <v>1883</v>
       </c>
       <c r="H64" s="12" t="n">
@@ -2768,26 +2768,26 @@
       <c r="A65" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B65" s="14" t="n">
+      <c r="B65" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="15" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E65" s="16" t="n">
+      <c r="E65" s="15" t="n">
         <v>1229597.47</v>
       </c>
-      <c r="F65" s="13" t="n">
+      <c r="F65" s="16" t="n">
         <v>102</v>
       </c>
-      <c r="G65" s="13" t="n">
+      <c r="G65" s="16" t="n">
         <v>86</v>
       </c>
       <c r="H65" s="17" t="n">
@@ -2798,26 +2798,26 @@
       <c r="A66" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B66" s="9" t="n">
+      <c r="B66" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E66" s="11" t="n">
+      <c r="E66" s="10" t="n">
         <v>1074409.09</v>
       </c>
-      <c r="F66" s="8" t="n">
+      <c r="F66" s="11" t="n">
         <v>265</v>
       </c>
-      <c r="G66" s="8" t="n">
+      <c r="G66" s="11" t="n">
         <v>265</v>
       </c>
       <c r="H66" s="12" t="n">
@@ -2828,26 +2828,26 @@
       <c r="A67" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B67" s="14" t="n">
+      <c r="B67" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E67" s="16" t="n">
+      <c r="E67" s="15" t="n">
         <v>70101479.81</v>
       </c>
-      <c r="F67" s="13" t="n">
+      <c r="F67" s="16" t="n">
         <v>8971</v>
       </c>
-      <c r="G67" s="13" t="n">
+      <c r="G67" s="16" t="n">
         <v>8209</v>
       </c>
       <c r="H67" s="17" t="n">
@@ -2858,26 +2858,26 @@
       <c r="A68" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B68" s="9" t="n">
+      <c r="B68" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E68" s="11" t="n">
+      <c r="E68" s="10" t="n">
         <v>8106694.82</v>
       </c>
-      <c r="F68" s="8" t="n">
+      <c r="F68" s="11" t="n">
         <v>654</v>
       </c>
-      <c r="G68" s="8" t="n">
+      <c r="G68" s="11" t="n">
         <v>566</v>
       </c>
       <c r="H68" s="12" t="n">
@@ -2888,26 +2888,26 @@
       <c r="A69" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B69" s="14" t="n">
+      <c r="B69" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C69" s="15" t="inlineStr">
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D69" s="15" t="inlineStr">
+      <c r="D69" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E69" s="16" t="n">
+      <c r="E69" s="15" t="n">
         <v>2485677.19</v>
       </c>
-      <c r="F69" s="13" t="n">
+      <c r="F69" s="16" t="n">
         <v>1173</v>
       </c>
-      <c r="G69" s="13" t="n">
+      <c r="G69" s="16" t="n">
         <v>1083</v>
       </c>
       <c r="H69" s="17" t="n">
@@ -2918,26 +2918,26 @@
       <c r="A70" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B70" s="9" t="n">
+      <c r="B70" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E70" s="11" t="n">
+      <c r="E70" s="10" t="n">
         <v>1407068.05</v>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F70" s="11" t="n">
         <v>98</v>
       </c>
-      <c r="G70" s="8" t="n">
+      <c r="G70" s="11" t="n">
         <v>85</v>
       </c>
       <c r="H70" s="12" t="n">
@@ -2948,26 +2948,26 @@
       <c r="A71" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B71" s="14" t="n">
+      <c r="B71" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="15" t="inlineStr">
+      <c r="C71" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D71" s="15" t="inlineStr">
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E71" s="16" t="n">
+      <c r="E71" s="15" t="n">
         <v>1051653.75</v>
       </c>
-      <c r="F71" s="13" t="n">
+      <c r="F71" s="16" t="n">
         <v>262</v>
       </c>
-      <c r="G71" s="13" t="n">
+      <c r="G71" s="16" t="n">
         <v>262</v>
       </c>
       <c r="H71" s="17" t="n">
@@ -2978,26 +2978,26 @@
       <c r="A72" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B72" s="9" t="n">
+      <c r="B72" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D72" s="10" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E72" s="11" t="n">
+      <c r="E72" s="10" t="n">
         <v>77435417.23999999</v>
       </c>
-      <c r="F72" s="8" t="n">
+      <c r="F72" s="11" t="n">
         <v>9319</v>
       </c>
-      <c r="G72" s="8" t="n">
+      <c r="G72" s="11" t="n">
         <v>8491</v>
       </c>
       <c r="H72" s="12" t="n">
@@ -3008,26 +3008,26 @@
       <c r="A73" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B73" s="14" t="n">
+      <c r="B73" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="15" t="inlineStr">
+      <c r="C73" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="D73" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E73" s="15" t="n">
         <v>7852147.48</v>
       </c>
-      <c r="F73" s="13" t="n">
+      <c r="F73" s="16" t="n">
         <v>658</v>
       </c>
-      <c r="G73" s="13" t="n">
+      <c r="G73" s="16" t="n">
         <v>566</v>
       </c>
       <c r="H73" s="17" t="n">
@@ -3038,26 +3038,26 @@
       <c r="A74" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B74" s="9" t="n">
+      <c r="B74" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E74" s="11" t="n">
+      <c r="E74" s="10" t="n">
         <v>3905027.53</v>
       </c>
-      <c r="F74" s="8" t="n">
+      <c r="F74" s="11" t="n">
         <v>2426</v>
       </c>
-      <c r="G74" s="8" t="n">
+      <c r="G74" s="11" t="n">
         <v>2350</v>
       </c>
       <c r="H74" s="12" t="n">
@@ -3068,26 +3068,26 @@
       <c r="A75" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B75" s="14" t="n">
+      <c r="B75" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="15" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="D75" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E75" s="16" t="n">
+      <c r="E75" s="15" t="n">
         <v>1422420.27</v>
       </c>
-      <c r="F75" s="13" t="n">
+      <c r="F75" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="G75" s="13" t="n">
+      <c r="G75" s="16" t="n">
         <v>90</v>
       </c>
       <c r="H75" s="17" t="n">
@@ -3098,26 +3098,26 @@
       <c r="A76" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B76" s="9" t="n">
+      <c r="B76" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E76" s="11" t="n">
+      <c r="E76" s="10" t="n">
         <v>1324152.49</v>
       </c>
-      <c r="F76" s="8" t="n">
+      <c r="F76" s="11" t="n">
         <v>265</v>
       </c>
-      <c r="G76" s="8" t="n">
+      <c r="G76" s="11" t="n">
         <v>261</v>
       </c>
       <c r="H76" s="12" t="n">
@@ -3128,26 +3128,26 @@
       <c r="A77" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B77" s="14" t="n">
+      <c r="B77" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C77" s="15" t="inlineStr">
+      <c r="C77" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="D77" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E77" s="16" t="n">
+      <c r="E77" s="15" t="n">
         <v>65902879.55</v>
       </c>
-      <c r="F77" s="13" t="n">
+      <c r="F77" s="16" t="n">
         <v>13582</v>
       </c>
-      <c r="G77" s="13" t="n">
+      <c r="G77" s="16" t="n">
         <v>8543</v>
       </c>
       <c r="H77" s="17" t="n">
@@ -3158,26 +3158,26 @@
       <c r="A78" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B78" s="9" t="n">
+      <c r="B78" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E78" s="11" t="n">
+      <c r="E78" s="10" t="n">
         <v>6889461.7</v>
       </c>
-      <c r="F78" s="8" t="n">
+      <c r="F78" s="11" t="n">
         <v>787</v>
       </c>
-      <c r="G78" s="8" t="n">
+      <c r="G78" s="11" t="n">
         <v>560</v>
       </c>
       <c r="H78" s="12" t="n">
@@ -3188,26 +3188,26 @@
       <c r="A79" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B79" s="14" t="n">
+      <c r="B79" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C79" s="15" t="inlineStr">
+      <c r="C79" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D79" s="15" t="inlineStr">
+      <c r="D79" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E79" s="16" t="n">
+      <c r="E79" s="15" t="n">
         <v>5092857.16</v>
       </c>
-      <c r="F79" s="13" t="n">
+      <c r="F79" s="16" t="n">
         <v>2997</v>
       </c>
-      <c r="G79" s="13" t="n">
+      <c r="G79" s="16" t="n">
         <v>2952</v>
       </c>
       <c r="H79" s="17" t="n">
@@ -3218,26 +3218,26 @@
       <c r="A80" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B80" s="9" t="n">
+      <c r="B80" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E80" s="11" t="n">
+      <c r="E80" s="10" t="n">
         <v>1407162.6</v>
       </c>
-      <c r="F80" s="8" t="n">
+      <c r="F80" s="11" t="n">
         <v>107</v>
       </c>
-      <c r="G80" s="8" t="n">
+      <c r="G80" s="11" t="n">
         <v>102</v>
       </c>
       <c r="H80" s="12" t="n">
@@ -3248,26 +3248,26 @@
       <c r="A81" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B81" s="14" t="n">
+      <c r="B81" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C81" s="15" t="inlineStr">
+      <c r="C81" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D81" s="15" t="inlineStr">
+      <c r="D81" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E81" s="16" t="n">
+      <c r="E81" s="15" t="n">
         <v>1101448.93</v>
       </c>
-      <c r="F81" s="13" t="n">
+      <c r="F81" s="16" t="n">
         <v>259</v>
       </c>
-      <c r="G81" s="13" t="n">
+      <c r="G81" s="16" t="n">
         <v>259</v>
       </c>
       <c r="H81" s="17" t="n">
@@ -3278,26 +3278,26 @@
       <c r="A82" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B82" s="9" t="n">
+      <c r="B82" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E82" s="11" t="n">
+      <c r="E82" s="10" t="n">
         <v>66577196.27</v>
       </c>
-      <c r="F82" s="8" t="n">
+      <c r="F82" s="11" t="n">
         <v>9370</v>
       </c>
-      <c r="G82" s="8" t="n">
+      <c r="G82" s="11" t="n">
         <v>8731</v>
       </c>
       <c r="H82" s="12" t="n">
@@ -3308,26 +3308,26 @@
       <c r="A83" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B83" s="14" t="n">
+      <c r="B83" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C83" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D83" s="15" t="inlineStr">
+      <c r="D83" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E83" s="16" t="n">
+      <c r="E83" s="15" t="n">
         <v>6730471.69</v>
       </c>
-      <c r="F83" s="13" t="n">
+      <c r="F83" s="16" t="n">
         <v>636</v>
       </c>
-      <c r="G83" s="13" t="n">
+      <c r="G83" s="16" t="n">
         <v>561</v>
       </c>
       <c r="H83" s="17" t="n">
@@ -3338,26 +3338,26 @@
       <c r="A84" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B84" s="9" t="n">
+      <c r="B84" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E84" s="11" t="n">
+      <c r="E84" s="10" t="n">
         <v>4479240.13</v>
       </c>
-      <c r="F84" s="8" t="n">
+      <c r="F84" s="11" t="n">
         <v>2871</v>
       </c>
-      <c r="G84" s="8" t="n">
+      <c r="G84" s="11" t="n">
         <v>2792</v>
       </c>
       <c r="H84" s="12" t="n">
@@ -3368,26 +3368,26 @@
       <c r="A85" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B85" s="14" t="n">
+      <c r="B85" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C85" s="15" t="inlineStr">
+      <c r="C85" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D85" s="15" t="inlineStr">
+      <c r="D85" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E85" s="16" t="n">
+      <c r="E85" s="15" t="n">
         <v>1696338.3</v>
       </c>
-      <c r="F85" s="13" t="n">
+      <c r="F85" s="16" t="n">
         <v>121</v>
       </c>
-      <c r="G85" s="13" t="n">
+      <c r="G85" s="16" t="n">
         <v>115</v>
       </c>
       <c r="H85" s="17" t="n">
@@ -3398,26 +3398,26 @@
       <c r="A86" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B86" s="9" t="n">
+      <c r="B86" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D86" s="10" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E86" s="11" t="n">
+      <c r="E86" s="10" t="n">
         <v>1105512.14</v>
       </c>
-      <c r="F86" s="8" t="n">
+      <c r="F86" s="11" t="n">
         <v>259</v>
       </c>
-      <c r="G86" s="8" t="n">
+      <c r="G86" s="11" t="n">
         <v>259</v>
       </c>
       <c r="H86" s="12" t="n">
@@ -3428,26 +3428,26 @@
       <c r="A87" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B87" s="14" t="n">
+      <c r="B87" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C87" s="15" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D87" s="15" t="inlineStr">
+      <c r="D87" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E87" s="16" t="n">
+      <c r="E87" s="15" t="n">
         <v>69342608.72</v>
       </c>
-      <c r="F87" s="13" t="n">
+      <c r="F87" s="16" t="n">
         <v>9387</v>
       </c>
-      <c r="G87" s="13" t="n">
+      <c r="G87" s="16" t="n">
         <v>8861</v>
       </c>
       <c r="H87" s="17" t="n">
@@ -3458,26 +3458,26 @@
       <c r="A88" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B88" s="9" t="n">
+      <c r="B88" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D88" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E88" s="11" t="n">
+      <c r="E88" s="10" t="n">
         <v>6913513.6</v>
       </c>
-      <c r="F88" s="8" t="n">
+      <c r="F88" s="11" t="n">
         <v>634</v>
       </c>
-      <c r="G88" s="8" t="n">
+      <c r="G88" s="11" t="n">
         <v>559</v>
       </c>
       <c r="H88" s="12" t="n">
@@ -3488,26 +3488,26 @@
       <c r="A89" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B89" s="14" t="n">
+      <c r="B89" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C89" s="15" t="inlineStr">
+      <c r="C89" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D89" s="15" t="inlineStr">
+      <c r="D89" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E89" s="16" t="n">
+      <c r="E89" s="15" t="n">
         <v>4864065.46</v>
       </c>
-      <c r="F89" s="13" t="n">
+      <c r="F89" s="16" t="n">
         <v>2971</v>
       </c>
-      <c r="G89" s="13" t="n">
+      <c r="G89" s="16" t="n">
         <v>2914</v>
       </c>
       <c r="H89" s="17" t="n">
@@ -3518,26 +3518,26 @@
       <c r="A90" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B90" s="9" t="n">
+      <c r="B90" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D90" s="10" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E90" s="11" t="n">
+      <c r="E90" s="10" t="n">
         <v>1615332.36</v>
       </c>
-      <c r="F90" s="8" t="n">
+      <c r="F90" s="11" t="n">
         <v>118</v>
       </c>
-      <c r="G90" s="8" t="n">
+      <c r="G90" s="11" t="n">
         <v>113</v>
       </c>
       <c r="H90" s="12" t="n">
@@ -3548,26 +3548,26 @@
       <c r="A91" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B91" s="14" t="n">
+      <c r="B91" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C91" s="15" t="inlineStr">
+      <c r="C91" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D91" s="15" t="inlineStr">
+      <c r="D91" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E91" s="16" t="n">
+      <c r="E91" s="15" t="n">
         <v>1098702.99</v>
       </c>
-      <c r="F91" s="13" t="n">
+      <c r="F91" s="16" t="n">
         <v>258</v>
       </c>
-      <c r="G91" s="13" t="n">
+      <c r="G91" s="16" t="n">
         <v>258</v>
       </c>
       <c r="H91" s="17" t="n">
@@ -3578,26 +3578,26 @@
       <c r="A92" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B92" s="9" t="n">
+      <c r="B92" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C92" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
+      <c r="D92" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E92" s="11" t="n">
+      <c r="E92" s="10" t="n">
         <v>71966795.23</v>
       </c>
-      <c r="F92" s="8" t="n">
+      <c r="F92" s="11" t="n">
         <v>9745</v>
       </c>
-      <c r="G92" s="8" t="n">
+      <c r="G92" s="11" t="n">
         <v>8844</v>
       </c>
       <c r="H92" s="12" t="n">
@@ -3608,26 +3608,26 @@
       <c r="A93" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B93" s="14" t="n">
+      <c r="B93" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C93" s="15" t="inlineStr">
+      <c r="C93" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D93" s="15" t="inlineStr">
+      <c r="D93" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E93" s="16" t="n">
+      <c r="E93" s="15" t="n">
         <v>7542830.13</v>
       </c>
-      <c r="F93" s="13" t="n">
+      <c r="F93" s="16" t="n">
         <v>696</v>
       </c>
-      <c r="G93" s="13" t="n">
+      <c r="G93" s="16" t="n">
         <v>550</v>
       </c>
       <c r="H93" s="17" t="n">
@@ -3638,26 +3638,26 @@
       <c r="A94" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B94" s="9" t="n">
+      <c r="B94" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C94" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D94" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E94" s="11" t="n">
+      <c r="E94" s="10" t="n">
         <v>4884926.98</v>
       </c>
-      <c r="F94" s="8" t="n">
+      <c r="F94" s="11" t="n">
         <v>2849</v>
       </c>
-      <c r="G94" s="8" t="n">
+      <c r="G94" s="11" t="n">
         <v>2775</v>
       </c>
       <c r="H94" s="12" t="n">
@@ -3668,26 +3668,26 @@
       <c r="A95" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B95" s="14" t="n">
+      <c r="B95" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C95" s="15" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D95" s="15" t="inlineStr">
+      <c r="D95" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E95" s="16" t="n">
+      <c r="E95" s="15" t="n">
         <v>1746607.07</v>
       </c>
-      <c r="F95" s="13" t="n">
+      <c r="F95" s="16" t="n">
         <v>134</v>
       </c>
-      <c r="G95" s="13" t="n">
+      <c r="G95" s="16" t="n">
         <v>116</v>
       </c>
       <c r="H95" s="17" t="n">
@@ -3698,26 +3698,26 @@
       <c r="A96" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B96" s="9" t="n">
+      <c r="B96" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D96" s="10" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E96" s="11" t="n">
+      <c r="E96" s="10" t="n">
         <v>1152274.68</v>
       </c>
-      <c r="F96" s="8" t="n">
+      <c r="F96" s="11" t="n">
         <v>255</v>
       </c>
-      <c r="G96" s="8" t="n">
+      <c r="G96" s="11" t="n">
         <v>255</v>
       </c>
       <c r="H96" s="12" t="n">
@@ -3728,26 +3728,26 @@
       <c r="A97" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B97" s="14" t="n">
+      <c r="B97" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C97" s="15" t="inlineStr">
+      <c r="C97" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D97" s="15" t="inlineStr">
+      <c r="D97" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E97" s="16" t="n">
+      <c r="E97" s="15" t="n">
         <v>75571652.94</v>
       </c>
-      <c r="F97" s="13" t="n">
+      <c r="F97" s="16" t="n">
         <v>9779</v>
       </c>
-      <c r="G97" s="13" t="n">
+      <c r="G97" s="16" t="n">
         <v>8974</v>
       </c>
       <c r="H97" s="17" t="n">
@@ -3758,26 +3758,26 @@
       <c r="A98" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B98" s="9" t="n">
+      <c r="B98" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C98" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D98" s="10" t="inlineStr">
+      <c r="D98" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E98" s="11" t="n">
+      <c r="E98" s="10" t="n">
         <v>7120411.06</v>
       </c>
-      <c r="F98" s="8" t="n">
+      <c r="F98" s="11" t="n">
         <v>640</v>
       </c>
-      <c r="G98" s="8" t="n">
+      <c r="G98" s="11" t="n">
         <v>541</v>
       </c>
       <c r="H98" s="12" t="n">
@@ -3788,26 +3788,26 @@
       <c r="A99" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B99" s="14" t="n">
+      <c r="B99" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C99" s="15" t="inlineStr">
+      <c r="C99" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D99" s="15" t="inlineStr">
+      <c r="D99" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E99" s="16" t="n">
+      <c r="E99" s="15" t="n">
         <v>4041038.72</v>
       </c>
-      <c r="F99" s="13" t="n">
+      <c r="F99" s="16" t="n">
         <v>2588</v>
       </c>
-      <c r="G99" s="13" t="n">
+      <c r="G99" s="16" t="n">
         <v>2558</v>
       </c>
       <c r="H99" s="17" t="n">
@@ -3818,26 +3818,26 @@
       <c r="A100" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B100" s="9" t="n">
+      <c r="B100" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="D100" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E100" s="11" t="n">
+      <c r="E100" s="10" t="n">
         <v>1832752.57</v>
       </c>
-      <c r="F100" s="8" t="n">
+      <c r="F100" s="11" t="n">
         <v>130</v>
       </c>
-      <c r="G100" s="8" t="n">
+      <c r="G100" s="11" t="n">
         <v>121</v>
       </c>
       <c r="H100" s="12" t="n">
@@ -3848,26 +3848,26 @@
       <c r="A101" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B101" s="14" t="n">
+      <c r="B101" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C101" s="15" t="inlineStr">
+      <c r="C101" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D101" s="15" t="inlineStr">
+      <c r="D101" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E101" s="16" t="n">
+      <c r="E101" s="15" t="n">
         <v>1161938.56</v>
       </c>
-      <c r="F101" s="13" t="n">
+      <c r="F101" s="16" t="n">
         <v>254</v>
       </c>
-      <c r="G101" s="13" t="n">
+      <c r="G101" s="16" t="n">
         <v>254</v>
       </c>
       <c r="H101" s="17" t="n">
@@ -3878,26 +3878,26 @@
       <c r="A102" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B102" s="9" t="n">
+      <c r="B102" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D102" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E102" s="11" t="n">
+      <c r="E102" s="10" t="n">
         <v>74534817.33</v>
       </c>
-      <c r="F102" s="8" t="n">
+      <c r="F102" s="11" t="n">
         <v>9640</v>
       </c>
-      <c r="G102" s="8" t="n">
+      <c r="G102" s="11" t="n">
         <v>8939</v>
       </c>
       <c r="H102" s="12" t="n">
@@ -3908,26 +3908,26 @@
       <c r="A103" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B103" s="14" t="n">
+      <c r="B103" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C103" s="15" t="inlineStr">
+      <c r="C103" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D103" s="15" t="inlineStr">
+      <c r="D103" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E103" s="16" t="n">
+      <c r="E103" s="15" t="n">
         <v>7313319.01</v>
       </c>
-      <c r="F103" s="13" t="n">
+      <c r="F103" s="16" t="n">
         <v>619</v>
       </c>
-      <c r="G103" s="13" t="n">
+      <c r="G103" s="16" t="n">
         <v>545</v>
       </c>
       <c r="H103" s="17" t="n">
@@ -3938,26 +3938,26 @@
       <c r="A104" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B104" s="9" t="n">
+      <c r="B104" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E104" s="11" t="n">
+      <c r="E104" s="10" t="n">
         <v>4898827.96</v>
       </c>
-      <c r="F104" s="8" t="n">
+      <c r="F104" s="11" t="n">
         <v>2867</v>
       </c>
-      <c r="G104" s="8" t="n">
+      <c r="G104" s="11" t="n">
         <v>2814</v>
       </c>
       <c r="H104" s="12" t="n">
@@ -3968,26 +3968,26 @@
       <c r="A105" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B105" s="14" t="n">
+      <c r="B105" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C105" s="15" t="inlineStr">
+      <c r="C105" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D105" s="15" t="inlineStr">
+      <c r="D105" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E105" s="16" t="n">
+      <c r="E105" s="15" t="n">
         <v>1737553.27</v>
       </c>
-      <c r="F105" s="13" t="n">
+      <c r="F105" s="16" t="n">
         <v>125</v>
       </c>
-      <c r="G105" s="13" t="n">
+      <c r="G105" s="16" t="n">
         <v>118</v>
       </c>
       <c r="H105" s="17" t="n">
@@ -3998,26 +3998,26 @@
       <c r="A106" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B106" s="9" t="n">
+      <c r="B106" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D106" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E106" s="11" t="n">
+      <c r="E106" s="10" t="n">
         <v>1137175.02</v>
       </c>
-      <c r="F106" s="8" t="n">
+      <c r="F106" s="11" t="n">
         <v>252</v>
       </c>
-      <c r="G106" s="8" t="n">
+      <c r="G106" s="11" t="n">
         <v>251</v>
       </c>
       <c r="H106" s="12" t="n">
@@ -4028,26 +4028,26 @@
       <c r="A107" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B107" s="14" t="n">
+      <c r="B107" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C107" s="15" t="inlineStr">
+      <c r="C107" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D107" s="15" t="inlineStr">
+      <c r="D107" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E107" s="16" t="n">
+      <c r="E107" s="15" t="n">
         <v>74474539.65000001</v>
       </c>
-      <c r="F107" s="13" t="n">
+      <c r="F107" s="16" t="n">
         <v>9461</v>
       </c>
-      <c r="G107" s="13" t="n">
+      <c r="G107" s="16" t="n">
         <v>8918</v>
       </c>
       <c r="H107" s="17" t="n">
@@ -4058,26 +4058,26 @@
       <c r="A108" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B108" s="9" t="n">
+      <c r="B108" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D108" s="10" t="inlineStr">
+      <c r="D108" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E108" s="11" t="n">
+      <c r="E108" s="10" t="n">
         <v>7201087.77</v>
       </c>
-      <c r="F108" s="8" t="n">
+      <c r="F108" s="11" t="n">
         <v>619</v>
       </c>
-      <c r="G108" s="8" t="n">
+      <c r="G108" s="11" t="n">
         <v>546</v>
       </c>
       <c r="H108" s="12" t="n">
@@ -4088,26 +4088,26 @@
       <c r="A109" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="14" t="n">
+      <c r="B109" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C109" s="15" t="inlineStr">
+      <c r="C109" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D109" s="15" t="inlineStr">
+      <c r="D109" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E109" s="16" t="n">
+      <c r="E109" s="15" t="n">
         <v>4868264.8</v>
       </c>
-      <c r="F109" s="13" t="n">
+      <c r="F109" s="16" t="n">
         <v>2842</v>
       </c>
-      <c r="G109" s="13" t="n">
+      <c r="G109" s="16" t="n">
         <v>2796</v>
       </c>
       <c r="H109" s="17" t="n">
@@ -4118,26 +4118,26 @@
       <c r="A110" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B110" s="9" t="n">
+      <c r="B110" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C110" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D110" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E110" s="11" t="n">
+      <c r="E110" s="10" t="n">
         <v>1817341.71</v>
       </c>
-      <c r="F110" s="8" t="n">
+      <c r="F110" s="11" t="n">
         <v>124</v>
       </c>
-      <c r="G110" s="8" t="n">
+      <c r="G110" s="11" t="n">
         <v>120</v>
       </c>
       <c r="H110" s="12" t="n">
@@ -4148,26 +4148,26 @@
       <c r="A111" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B111" s="14" t="n">
+      <c r="B111" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C111" s="15" t="inlineStr">
+      <c r="C111" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D111" s="15" t="inlineStr">
+      <c r="D111" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E111" s="16" t="n">
+      <c r="E111" s="15" t="n">
         <v>1124277.81</v>
       </c>
-      <c r="F111" s="13" t="n">
+      <c r="F111" s="16" t="n">
         <v>251</v>
       </c>
-      <c r="G111" s="13" t="n">
+      <c r="G111" s="16" t="n">
         <v>249</v>
       </c>
       <c r="H111" s="17" t="n">
@@ -4178,26 +4178,26 @@
       <c r="A112" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B112" s="9" t="n">
+      <c r="B112" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C112" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D112" s="10" t="inlineStr">
+      <c r="D112" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E112" s="11" t="n">
+      <c r="E112" s="10" t="n">
         <v>98363183.73</v>
       </c>
-      <c r="F112" s="8" t="n">
+      <c r="F112" s="11" t="n">
         <v>9792</v>
       </c>
-      <c r="G112" s="8" t="n">
+      <c r="G112" s="11" t="n">
         <v>9007</v>
       </c>
       <c r="H112" s="12" t="n">
@@ -4208,26 +4208,26 @@
       <c r="A113" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B113" s="14" t="n">
+      <c r="B113" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C113" s="15" t="inlineStr">
+      <c r="C113" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D113" s="15" t="inlineStr">
+      <c r="D113" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E113" s="16" t="n">
+      <c r="E113" s="15" t="n">
         <v>9953868.720000001</v>
       </c>
-      <c r="F113" s="13" t="n">
+      <c r="F113" s="16" t="n">
         <v>626</v>
       </c>
-      <c r="G113" s="13" t="n">
+      <c r="G113" s="16" t="n">
         <v>540</v>
       </c>
       <c r="H113" s="17" t="n">
@@ -4238,26 +4238,26 @@
       <c r="A114" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B114" s="9" t="n">
+      <c r="B114" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C114" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D114" s="10" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E114" s="11" t="n">
+      <c r="E114" s="10" t="n">
         <v>7794857.18</v>
       </c>
-      <c r="F114" s="8" t="n">
+      <c r="F114" s="11" t="n">
         <v>2821</v>
       </c>
-      <c r="G114" s="8" t="n">
+      <c r="G114" s="11" t="n">
         <v>2771</v>
       </c>
       <c r="H114" s="12" t="n">
@@ -4268,26 +4268,26 @@
       <c r="A115" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B115" s="14" t="n">
+      <c r="B115" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C115" s="15" t="inlineStr">
+      <c r="C115" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D115" s="15" t="inlineStr">
+      <c r="D115" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E115" s="16" t="n">
+      <c r="E115" s="15" t="n">
         <v>2471506.22</v>
       </c>
-      <c r="F115" s="13" t="n">
+      <c r="F115" s="16" t="n">
         <v>125</v>
       </c>
-      <c r="G115" s="13" t="n">
+      <c r="G115" s="16" t="n">
         <v>119</v>
       </c>
       <c r="H115" s="17" t="n">
@@ -4298,26 +4298,26 @@
       <c r="A116" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B116" s="9" t="n">
+      <c r="B116" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D116" s="10" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E116" s="11" t="n">
+      <c r="E116" s="10" t="n">
         <v>1656643.98</v>
       </c>
-      <c r="F116" s="8" t="n">
+      <c r="F116" s="11" t="n">
         <v>249</v>
       </c>
-      <c r="G116" s="8" t="n">
+      <c r="G116" s="11" t="n">
         <v>248</v>
       </c>
       <c r="H116" s="12" t="n">
@@ -4328,26 +4328,26 @@
       <c r="A117" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B117" s="14" t="n">
+      <c r="B117" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C117" s="15" t="inlineStr">
+      <c r="C117" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D117" s="15" t="inlineStr">
+      <c r="D117" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E117" s="16" t="n">
+      <c r="E117" s="15" t="n">
         <v>145237583.88</v>
       </c>
-      <c r="F117" s="13" t="n">
+      <c r="F117" s="16" t="n">
         <v>27115</v>
       </c>
-      <c r="G117" s="13" t="n">
+      <c r="G117" s="16" t="n">
         <v>8992</v>
       </c>
       <c r="H117" s="17" t="n">
@@ -4358,26 +4358,26 @@
       <c r="A118" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B118" s="9" t="n">
+      <c r="B118" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C118" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D118" s="10" t="inlineStr">
+      <c r="D118" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E118" s="11" t="n">
+      <c r="E118" s="10" t="n">
         <v>14015353.19</v>
       </c>
-      <c r="F118" s="8" t="n">
+      <c r="F118" s="11" t="n">
         <v>1747</v>
       </c>
-      <c r="G118" s="8" t="n">
+      <c r="G118" s="11" t="n">
         <v>541</v>
       </c>
       <c r="H118" s="12" t="n">
@@ -4388,26 +4388,26 @@
       <c r="A119" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B119" s="14" t="n">
+      <c r="B119" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C119" s="15" t="inlineStr">
+      <c r="C119" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D119" s="15" t="inlineStr">
+      <c r="D119" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E119" s="16" t="n">
+      <c r="E119" s="15" t="n">
         <v>4545019.61</v>
       </c>
-      <c r="F119" s="13" t="n">
+      <c r="F119" s="16" t="n">
         <v>2833</v>
       </c>
-      <c r="G119" s="13" t="n">
+      <c r="G119" s="16" t="n">
         <v>2686</v>
       </c>
       <c r="H119" s="17" t="n">
@@ -4418,26 +4418,26 @@
       <c r="A120" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B120" s="9" t="n">
+      <c r="B120" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C120" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D120" s="10" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E120" s="11" t="n">
+      <c r="E120" s="10" t="n">
         <v>3212239.94</v>
       </c>
-      <c r="F120" s="8" t="n">
+      <c r="F120" s="11" t="n">
         <v>353</v>
       </c>
-      <c r="G120" s="8" t="n">
+      <c r="G120" s="11" t="n">
         <v>118</v>
       </c>
       <c r="H120" s="12" t="n">
@@ -4448,26 +4448,26 @@
       <c r="A121" s="13" t="n">
         <v>2023</v>
       </c>
-      <c r="B121" s="14" t="n">
+      <c r="B121" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C121" s="15" t="inlineStr">
+      <c r="C121" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D121" s="15" t="inlineStr">
+      <c r="D121" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E121" s="16" t="n">
+      <c r="E121" s="15" t="n">
         <v>2338707.64</v>
       </c>
-      <c r="F121" s="13" t="n">
+      <c r="F121" s="16" t="n">
         <v>694</v>
       </c>
-      <c r="G121" s="13" t="n">
+      <c r="G121" s="16" t="n">
         <v>254</v>
       </c>
       <c r="H121" s="17" t="n">
@@ -4478,26 +4478,26 @@
       <c r="A122" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B122" s="9" t="n">
+      <c r="B122" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="C122" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D122" s="10" t="inlineStr">
+      <c r="D122" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E122" s="11" t="n">
+      <c r="E122" s="10" t="n">
         <v>82647087.64</v>
       </c>
-      <c r="F122" s="8" t="n">
+      <c r="F122" s="11" t="n">
         <v>13307</v>
       </c>
-      <c r="G122" s="8" t="n">
+      <c r="G122" s="11" t="n">
         <v>8724</v>
       </c>
       <c r="H122" s="12" t="n">
@@ -4508,26 +4508,26 @@
       <c r="A123" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B123" s="14" t="n">
+      <c r="B123" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C123" s="15" t="inlineStr">
+      <c r="C123" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D123" s="15" t="inlineStr">
+      <c r="D123" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E123" s="16" t="n">
+      <c r="E123" s="15" t="n">
         <v>7880592.55</v>
       </c>
-      <c r="F123" s="13" t="n">
+      <c r="F123" s="16" t="n">
         <v>615</v>
       </c>
-      <c r="G123" s="13" t="n">
+      <c r="G123" s="16" t="n">
         <v>543</v>
       </c>
       <c r="H123" s="17" t="n">
@@ -4538,26 +4538,26 @@
       <c r="A124" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B124" s="9" t="n">
+      <c r="B124" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C124" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D124" s="10" t="inlineStr">
+      <c r="D124" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E124" s="11" t="n">
+      <c r="E124" s="10" t="n">
         <v>2972936.44</v>
       </c>
-      <c r="F124" s="8" t="n">
+      <c r="F124" s="11" t="n">
         <v>2304</v>
       </c>
-      <c r="G124" s="8" t="n">
+      <c r="G124" s="11" t="n">
         <v>2243</v>
       </c>
       <c r="H124" s="12" t="n">
@@ -4568,26 +4568,26 @@
       <c r="A125" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B125" s="14" t="n">
+      <c r="B125" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C125" s="15" t="inlineStr">
+      <c r="C125" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D125" s="15" t="inlineStr">
+      <c r="D125" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E125" s="16" t="n">
+      <c r="E125" s="15" t="n">
         <v>1815825.98</v>
       </c>
-      <c r="F125" s="13" t="n">
+      <c r="F125" s="16" t="n">
         <v>127</v>
       </c>
-      <c r="G125" s="13" t="n">
+      <c r="G125" s="16" t="n">
         <v>118</v>
       </c>
       <c r="H125" s="17" t="n">
@@ -4598,26 +4598,26 @@
       <c r="A126" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B126" s="9" t="n">
+      <c r="B126" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C126" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="D126" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E126" s="11" t="n">
+      <c r="E126" s="10" t="n">
         <v>1120139.24</v>
       </c>
-      <c r="F126" s="8" t="n">
+      <c r="F126" s="11" t="n">
         <v>245</v>
       </c>
-      <c r="G126" s="8" t="n">
+      <c r="G126" s="11" t="n">
         <v>245</v>
       </c>
       <c r="H126" s="12" t="n">
@@ -4628,26 +4628,26 @@
       <c r="A127" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B127" s="14" t="n">
+      <c r="B127" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C127" s="15" t="inlineStr">
+      <c r="C127" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D127" s="15" t="inlineStr">
+      <c r="D127" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E127" s="16" t="n">
+      <c r="E127" s="15" t="n">
         <v>75441273.69</v>
       </c>
-      <c r="F127" s="13" t="n">
+      <c r="F127" s="16" t="n">
         <v>9532</v>
       </c>
-      <c r="G127" s="13" t="n">
+      <c r="G127" s="16" t="n">
         <v>8925</v>
       </c>
       <c r="H127" s="17" t="n">
@@ -4658,26 +4658,26 @@
       <c r="A128" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B128" s="9" t="n">
+      <c r="B128" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="C128" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D128" s="10" t="inlineStr">
+      <c r="D128" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E128" s="11" t="n">
+      <c r="E128" s="10" t="n">
         <v>7995453.78</v>
       </c>
-      <c r="F128" s="8" t="n">
+      <c r="F128" s="11" t="n">
         <v>625</v>
       </c>
-      <c r="G128" s="8" t="n">
+      <c r="G128" s="11" t="n">
         <v>540</v>
       </c>
       <c r="H128" s="12" t="n">
@@ -4688,26 +4688,26 @@
       <c r="A129" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B129" s="14" t="n">
+      <c r="B129" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C129" s="15" t="inlineStr">
+      <c r="C129" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D129" s="15" t="inlineStr">
+      <c r="D129" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E129" s="16" t="n">
+      <c r="E129" s="15" t="n">
         <v>1843015.36</v>
       </c>
-      <c r="F129" s="13" t="n">
+      <c r="F129" s="16" t="n">
         <v>138</v>
       </c>
-      <c r="G129" s="13" t="n">
+      <c r="G129" s="16" t="n">
         <v>125</v>
       </c>
       <c r="H129" s="17" t="n">
@@ -4718,26 +4718,26 @@
       <c r="A130" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B130" s="9" t="n">
+      <c r="B130" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="C130" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D130" s="10" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E130" s="11" t="n">
+      <c r="E130" s="10" t="n">
         <v>1211709.96</v>
       </c>
-      <c r="F130" s="8" t="n">
+      <c r="F130" s="11" t="n">
         <v>1176</v>
       </c>
-      <c r="G130" s="8" t="n">
+      <c r="G130" s="11" t="n">
         <v>1139</v>
       </c>
       <c r="H130" s="12" t="n">
@@ -4748,26 +4748,26 @@
       <c r="A131" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B131" s="14" t="n">
+      <c r="B131" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C131" s="15" t="inlineStr">
+      <c r="C131" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D131" s="15" t="inlineStr">
+      <c r="D131" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E131" s="16" t="n">
+      <c r="E131" s="15" t="n">
         <v>1112014.74</v>
       </c>
-      <c r="F131" s="13" t="n">
+      <c r="F131" s="16" t="n">
         <v>248</v>
       </c>
-      <c r="G131" s="13" t="n">
+      <c r="G131" s="16" t="n">
         <v>248</v>
       </c>
       <c r="H131" s="17" t="n">
@@ -4778,26 +4778,26 @@
       <c r="A132" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B132" s="9" t="n">
+      <c r="B132" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="C132" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D132" s="10" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E132" s="11" t="n">
+      <c r="E132" s="10" t="n">
         <v>93831201.81</v>
       </c>
-      <c r="F132" s="8" t="n">
+      <c r="F132" s="11" t="n">
         <v>9581</v>
       </c>
-      <c r="G132" s="8" t="n">
+      <c r="G132" s="11" t="n">
         <v>8960</v>
       </c>
       <c r="H132" s="12" t="n">
@@ -4808,26 +4808,26 @@
       <c r="A133" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B133" s="14" t="n">
+      <c r="B133" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C133" s="15" t="inlineStr">
+      <c r="C133" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D133" s="15" t="inlineStr">
+      <c r="D133" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E133" s="16" t="n">
+      <c r="E133" s="15" t="n">
         <v>8984818.189999999</v>
       </c>
-      <c r="F133" s="13" t="n">
+      <c r="F133" s="16" t="n">
         <v>619</v>
       </c>
-      <c r="G133" s="13" t="n">
+      <c r="G133" s="16" t="n">
         <v>545</v>
       </c>
       <c r="H133" s="17" t="n">
@@ -4838,26 +4838,26 @@
       <c r="A134" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B134" s="9" t="n">
+      <c r="B134" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="C134" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D134" s="10" t="inlineStr">
+      <c r="D134" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E134" s="11" t="n">
+      <c r="E134" s="10" t="n">
         <v>3190566.4</v>
       </c>
-      <c r="F134" s="8" t="n">
+      <c r="F134" s="11" t="n">
         <v>2501</v>
       </c>
-      <c r="G134" s="8" t="n">
+      <c r="G134" s="11" t="n">
         <v>2477</v>
       </c>
       <c r="H134" s="12" t="n">
@@ -4868,26 +4868,26 @@
       <c r="A135" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B135" s="14" t="n">
+      <c r="B135" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C135" s="15" t="inlineStr">
+      <c r="C135" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D135" s="15" t="inlineStr">
+      <c r="D135" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E135" s="16" t="n">
+      <c r="E135" s="15" t="n">
         <v>2069890.66</v>
       </c>
-      <c r="F135" s="13" t="n">
+      <c r="F135" s="16" t="n">
         <v>134</v>
       </c>
-      <c r="G135" s="13" t="n">
+      <c r="G135" s="16" t="n">
         <v>128</v>
       </c>
       <c r="H135" s="17" t="n">
@@ -4898,26 +4898,26 @@
       <c r="A136" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B136" s="9" t="n">
+      <c r="B136" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="C136" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D136" s="10" t="inlineStr">
+      <c r="D136" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E136" s="11" t="n">
+      <c r="E136" s="10" t="n">
         <v>1249543.15</v>
       </c>
-      <c r="F136" s="8" t="n">
+      <c r="F136" s="11" t="n">
         <v>247</v>
       </c>
-      <c r="G136" s="8" t="n">
+      <c r="G136" s="11" t="n">
         <v>247</v>
       </c>
       <c r="H136" s="12" t="n">
@@ -4928,26 +4928,26 @@
       <c r="A137" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B137" s="14" t="n">
+      <c r="B137" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C137" s="15" t="inlineStr">
+      <c r="C137" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D137" s="15" t="inlineStr">
+      <c r="D137" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E137" s="16" t="n">
+      <c r="E137" s="15" t="n">
         <v>82381118.92</v>
       </c>
-      <c r="F137" s="13" t="n">
+      <c r="F137" s="16" t="n">
         <v>9834</v>
       </c>
-      <c r="G137" s="13" t="n">
+      <c r="G137" s="16" t="n">
         <v>8968</v>
       </c>
       <c r="H137" s="17" t="n">
@@ -4958,26 +4958,26 @@
       <c r="A138" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B138" s="9" t="n">
+      <c r="B138" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="C138" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D138" s="10" t="inlineStr">
+      <c r="D138" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E138" s="11" t="n">
+      <c r="E138" s="10" t="n">
         <v>8324970.82</v>
       </c>
-      <c r="F138" s="8" t="n">
+      <c r="F138" s="11" t="n">
         <v>628</v>
       </c>
-      <c r="G138" s="8" t="n">
+      <c r="G138" s="11" t="n">
         <v>541</v>
       </c>
       <c r="H138" s="12" t="n">
@@ -4988,26 +4988,26 @@
       <c r="A139" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B139" s="14" t="n">
+      <c r="B139" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C139" s="15" t="inlineStr">
+      <c r="C139" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D139" s="15" t="inlineStr">
+      <c r="D139" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E139" s="16" t="n">
+      <c r="E139" s="15" t="n">
         <v>4947844.68</v>
       </c>
-      <c r="F139" s="13" t="n">
+      <c r="F139" s="16" t="n">
         <v>236</v>
       </c>
-      <c r="G139" s="13" t="n">
+      <c r="G139" s="16" t="n">
         <v>231</v>
       </c>
       <c r="H139" s="17" t="n">
@@ -5018,26 +5018,26 @@
       <c r="A140" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B140" s="9" t="n">
+      <c r="B140" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="C140" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D140" s="10" t="inlineStr">
+      <c r="D140" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E140" s="11" t="n">
+      <c r="E140" s="10" t="n">
         <v>4211561.14</v>
       </c>
-      <c r="F140" s="8" t="n">
+      <c r="F140" s="11" t="n">
         <v>3094</v>
       </c>
-      <c r="G140" s="8" t="n">
+      <c r="G140" s="11" t="n">
         <v>3024</v>
       </c>
       <c r="H140" s="12" t="n">
@@ -5048,26 +5048,26 @@
       <c r="A141" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B141" s="14" t="n">
+      <c r="B141" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C141" s="15" t="inlineStr">
+      <c r="C141" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D141" s="15" t="inlineStr">
+      <c r="D141" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E141" s="16" t="n">
+      <c r="E141" s="15" t="n">
         <v>1147594.79</v>
       </c>
-      <c r="F141" s="13" t="n">
+      <c r="F141" s="16" t="n">
         <v>258</v>
       </c>
-      <c r="G141" s="13" t="n">
+      <c r="G141" s="16" t="n">
         <v>246</v>
       </c>
       <c r="H141" s="17" t="n">
@@ -5078,26 +5078,26 @@
       <c r="A142" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B142" s="9" t="n">
+      <c r="B142" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C142" s="10" t="inlineStr">
+      <c r="C142" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D142" s="10" t="inlineStr">
+      <c r="D142" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E142" s="11" t="n">
+      <c r="E142" s="10" t="n">
         <v>82555775.64</v>
       </c>
-      <c r="F142" s="8" t="n">
+      <c r="F142" s="11" t="n">
         <v>9594</v>
       </c>
-      <c r="G142" s="8" t="n">
+      <c r="G142" s="11" t="n">
         <v>8973</v>
       </c>
       <c r="H142" s="12" t="n">
@@ -5108,26 +5108,26 @@
       <c r="A143" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B143" s="14" t="n">
+      <c r="B143" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C143" s="15" t="inlineStr">
+      <c r="C143" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D143" s="15" t="inlineStr">
+      <c r="D143" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E143" s="16" t="n">
+      <c r="E143" s="15" t="n">
         <v>7813667.58</v>
       </c>
-      <c r="F143" s="13" t="n">
+      <c r="F143" s="16" t="n">
         <v>598</v>
       </c>
-      <c r="G143" s="13" t="n">
+      <c r="G143" s="16" t="n">
         <v>532</v>
       </c>
       <c r="H143" s="17" t="n">
@@ -5138,26 +5138,26 @@
       <c r="A144" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B144" s="9" t="n">
+      <c r="B144" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C144" s="10" t="inlineStr">
+      <c r="C144" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D144" s="10" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E144" s="11" t="n">
+      <c r="E144" s="10" t="n">
         <v>5285002.03</v>
       </c>
-      <c r="F144" s="8" t="n">
+      <c r="F144" s="11" t="n">
         <v>3333</v>
       </c>
-      <c r="G144" s="8" t="n">
+      <c r="G144" s="11" t="n">
         <v>3233</v>
       </c>
       <c r="H144" s="12" t="n">
@@ -5168,26 +5168,26 @@
       <c r="A145" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B145" s="14" t="n">
+      <c r="B145" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C145" s="15" t="inlineStr">
+      <c r="C145" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D145" s="15" t="inlineStr">
+      <c r="D145" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E145" s="16" t="n">
+      <c r="E145" s="15" t="n">
         <v>2089274.73</v>
       </c>
-      <c r="F145" s="13" t="n">
+      <c r="F145" s="16" t="n">
         <v>144</v>
       </c>
-      <c r="G145" s="13" t="n">
+      <c r="G145" s="16" t="n">
         <v>137</v>
       </c>
       <c r="H145" s="17" t="n">
@@ -5198,26 +5198,26 @@
       <c r="A146" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B146" s="9" t="n">
+      <c r="B146" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="C146" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D146" s="10" t="inlineStr">
+      <c r="D146" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E146" s="11" t="n">
+      <c r="E146" s="10" t="n">
         <v>1127065.15</v>
       </c>
-      <c r="F146" s="8" t="n">
+      <c r="F146" s="11" t="n">
         <v>245</v>
       </c>
-      <c r="G146" s="8" t="n">
+      <c r="G146" s="11" t="n">
         <v>241</v>
       </c>
       <c r="H146" s="12" t="n">
@@ -5228,26 +5228,26 @@
       <c r="A147" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B147" s="14" t="n">
+      <c r="B147" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C147" s="15" t="inlineStr">
+      <c r="C147" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D147" s="15" t="inlineStr">
+      <c r="D147" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E147" s="16" t="n">
+      <c r="E147" s="15" t="n">
         <v>81429562.59</v>
       </c>
-      <c r="F147" s="13" t="n">
+      <c r="F147" s="16" t="n">
         <v>9621</v>
       </c>
-      <c r="G147" s="13" t="n">
+      <c r="G147" s="16" t="n">
         <v>9022</v>
       </c>
       <c r="H147" s="17" t="n">
@@ -5258,26 +5258,26 @@
       <c r="A148" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B148" s="9" t="n">
+      <c r="B148" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C148" s="10" t="inlineStr">
+      <c r="C148" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D148" s="10" t="inlineStr">
+      <c r="D148" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E148" s="11" t="n">
+      <c r="E148" s="10" t="n">
         <v>8231596.58</v>
       </c>
-      <c r="F148" s="8" t="n">
+      <c r="F148" s="11" t="n">
         <v>623</v>
       </c>
-      <c r="G148" s="8" t="n">
+      <c r="G148" s="11" t="n">
         <v>542</v>
       </c>
       <c r="H148" s="12" t="n">
@@ -5288,26 +5288,26 @@
       <c r="A149" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B149" s="14" t="n">
+      <c r="B149" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C149" s="15" t="inlineStr">
+      <c r="C149" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D149" s="15" t="inlineStr">
+      <c r="D149" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E149" s="16" t="n">
+      <c r="E149" s="15" t="n">
         <v>5058191.39</v>
       </c>
-      <c r="F149" s="13" t="n">
+      <c r="F149" s="16" t="n">
         <v>3255</v>
       </c>
-      <c r="G149" s="13" t="n">
+      <c r="G149" s="16" t="n">
         <v>3200</v>
       </c>
       <c r="H149" s="17" t="n">
@@ -5318,26 +5318,26 @@
       <c r="A150" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B150" s="9" t="n">
+      <c r="B150" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C150" s="10" t="inlineStr">
+      <c r="C150" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D150" s="10" t="inlineStr">
+      <c r="D150" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E150" s="11" t="n">
+      <c r="E150" s="10" t="n">
         <v>1975335.92</v>
       </c>
-      <c r="F150" s="8" t="n">
+      <c r="F150" s="11" t="n">
         <v>138</v>
       </c>
-      <c r="G150" s="8" t="n">
+      <c r="G150" s="11" t="n">
         <v>135</v>
       </c>
       <c r="H150" s="12" t="n">
@@ -5348,26 +5348,26 @@
       <c r="A151" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B151" s="14" t="n">
+      <c r="B151" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C151" s="15" t="inlineStr">
+      <c r="C151" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D151" s="15" t="inlineStr">
+      <c r="D151" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E151" s="16" t="n">
+      <c r="E151" s="15" t="n">
         <v>1126123.12</v>
       </c>
-      <c r="F151" s="13" t="n">
+      <c r="F151" s="16" t="n">
         <v>241</v>
       </c>
-      <c r="G151" s="13" t="n">
+      <c r="G151" s="16" t="n">
         <v>241</v>
       </c>
       <c r="H151" s="17" t="n">
@@ -5378,26 +5378,26 @@
       <c r="A152" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B152" s="9" t="n">
+      <c r="B152" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C152" s="10" t="inlineStr">
+      <c r="C152" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D152" s="10" t="inlineStr">
+      <c r="D152" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E152" s="11" t="n">
+      <c r="E152" s="10" t="n">
         <v>83189251.11</v>
       </c>
-      <c r="F152" s="8" t="n">
+      <c r="F152" s="11" t="n">
         <v>10462</v>
       </c>
-      <c r="G152" s="8" t="n">
+      <c r="G152" s="11" t="n">
         <v>9007</v>
       </c>
       <c r="H152" s="12" t="n">
@@ -5408,26 +5408,26 @@
       <c r="A153" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B153" s="14" t="n">
+      <c r="B153" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C153" s="15" t="inlineStr">
+      <c r="C153" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D153" s="15" t="inlineStr">
+      <c r="D153" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E153" s="16" t="n">
+      <c r="E153" s="15" t="n">
         <v>8208271.11</v>
       </c>
-      <c r="F153" s="13" t="n">
+      <c r="F153" s="16" t="n">
         <v>687</v>
       </c>
-      <c r="G153" s="13" t="n">
+      <c r="G153" s="16" t="n">
         <v>537</v>
       </c>
       <c r="H153" s="17" t="n">
@@ -5438,26 +5438,26 @@
       <c r="A154" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B154" s="9" t="n">
+      <c r="B154" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C154" s="10" t="inlineStr">
+      <c r="C154" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D154" s="10" t="inlineStr">
+      <c r="D154" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E154" s="11" t="n">
+      <c r="E154" s="10" t="n">
         <v>5245505.86</v>
       </c>
-      <c r="F154" s="8" t="n">
+      <c r="F154" s="11" t="n">
         <v>3268</v>
       </c>
-      <c r="G154" s="8" t="n">
+      <c r="G154" s="11" t="n">
         <v>3221</v>
       </c>
       <c r="H154" s="12" t="n">
@@ -5468,26 +5468,26 @@
       <c r="A155" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B155" s="14" t="n">
+      <c r="B155" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C155" s="15" t="inlineStr">
+      <c r="C155" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D155" s="15" t="inlineStr">
+      <c r="D155" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E155" s="16" t="n">
+      <c r="E155" s="15" t="n">
         <v>2110814.98</v>
       </c>
-      <c r="F155" s="13" t="n">
+      <c r="F155" s="16" t="n">
         <v>147</v>
       </c>
-      <c r="G155" s="13" t="n">
+      <c r="G155" s="16" t="n">
         <v>144</v>
       </c>
       <c r="H155" s="17" t="n">
@@ -5498,26 +5498,26 @@
       <c r="A156" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B156" s="9" t="n">
+      <c r="B156" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C156" s="10" t="inlineStr">
+      <c r="C156" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D156" s="10" t="inlineStr">
+      <c r="D156" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E156" s="11" t="n">
+      <c r="E156" s="10" t="n">
         <v>1110933.42</v>
       </c>
-      <c r="F156" s="8" t="n">
+      <c r="F156" s="11" t="n">
         <v>237</v>
       </c>
-      <c r="G156" s="8" t="n">
+      <c r="G156" s="11" t="n">
         <v>237</v>
       </c>
       <c r="H156" s="12" t="n">
@@ -5528,26 +5528,26 @@
       <c r="A157" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B157" s="14" t="n">
+      <c r="B157" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C157" s="15" t="inlineStr">
+      <c r="C157" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D157" s="15" t="inlineStr">
+      <c r="D157" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E157" s="16" t="n">
+      <c r="E157" s="15" t="n">
         <v>80982609.15000001</v>
       </c>
-      <c r="F157" s="13" t="n">
+      <c r="F157" s="16" t="n">
         <v>9787</v>
       </c>
-      <c r="G157" s="13" t="n">
+      <c r="G157" s="16" t="n">
         <v>9054</v>
       </c>
       <c r="H157" s="17" t="n">
@@ -5558,26 +5558,26 @@
       <c r="A158" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B158" s="9" t="n">
+      <c r="B158" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C158" s="10" t="inlineStr">
+      <c r="C158" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D158" s="10" t="inlineStr">
+      <c r="D158" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E158" s="11" t="n">
+      <c r="E158" s="10" t="n">
         <v>7667087.63</v>
       </c>
-      <c r="F158" s="8" t="n">
+      <c r="F158" s="11" t="n">
         <v>632</v>
       </c>
-      <c r="G158" s="8" t="n">
+      <c r="G158" s="11" t="n">
         <v>537</v>
       </c>
       <c r="H158" s="12" t="n">
@@ -5588,26 +5588,26 @@
       <c r="A159" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="14" t="n">
+      <c r="B159" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C159" s="15" t="inlineStr">
+      <c r="C159" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D159" s="15" t="inlineStr">
+      <c r="D159" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E159" s="16" t="n">
+      <c r="E159" s="15" t="n">
         <v>3505116.56</v>
       </c>
-      <c r="F159" s="13" t="n">
+      <c r="F159" s="16" t="n">
         <v>2928</v>
       </c>
-      <c r="G159" s="13" t="n">
+      <c r="G159" s="16" t="n">
         <v>2814</v>
       </c>
       <c r="H159" s="17" t="n">
@@ -5618,26 +5618,26 @@
       <c r="A160" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B160" s="9" t="n">
+      <c r="B160" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C160" s="10" t="inlineStr">
+      <c r="C160" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D160" s="10" t="inlineStr">
+      <c r="D160" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E160" s="11" t="n">
+      <c r="E160" s="10" t="n">
         <v>2061352.43</v>
       </c>
-      <c r="F160" s="8" t="n">
+      <c r="F160" s="11" t="n">
         <v>140</v>
       </c>
-      <c r="G160" s="8" t="n">
+      <c r="G160" s="11" t="n">
         <v>136</v>
       </c>
       <c r="H160" s="12" t="n">
@@ -5648,26 +5648,26 @@
       <c r="A161" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B161" s="14" t="n">
+      <c r="B161" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C161" s="15" t="inlineStr">
+      <c r="C161" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D161" s="15" t="inlineStr">
+      <c r="D161" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E161" s="16" t="n">
+      <c r="E161" s="15" t="n">
         <v>1101651.31</v>
       </c>
-      <c r="F161" s="13" t="n">
+      <c r="F161" s="16" t="n">
         <v>235</v>
       </c>
-      <c r="G161" s="13" t="n">
+      <c r="G161" s="16" t="n">
         <v>235</v>
       </c>
       <c r="H161" s="17" t="n">
@@ -5678,26 +5678,26 @@
       <c r="A162" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B162" s="9" t="n">
+      <c r="B162" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C162" s="10" t="inlineStr">
+      <c r="C162" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D162" s="10" t="inlineStr">
+      <c r="D162" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E162" s="11" t="n">
+      <c r="E162" s="10" t="n">
         <v>81731673.36</v>
       </c>
-      <c r="F162" s="8" t="n">
+      <c r="F162" s="11" t="n">
         <v>9761</v>
       </c>
-      <c r="G162" s="8" t="n">
+      <c r="G162" s="11" t="n">
         <v>9070</v>
       </c>
       <c r="H162" s="12" t="n">
@@ -5708,26 +5708,26 @@
       <c r="A163" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B163" s="14" t="n">
+      <c r="B163" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C163" s="15" t="inlineStr">
+      <c r="C163" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D163" s="15" t="inlineStr">
+      <c r="D163" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E163" s="16" t="n">
+      <c r="E163" s="15" t="n">
         <v>7911731.1</v>
       </c>
-      <c r="F163" s="13" t="n">
+      <c r="F163" s="16" t="n">
         <v>624</v>
       </c>
-      <c r="G163" s="13" t="n">
+      <c r="G163" s="16" t="n">
         <v>538</v>
       </c>
       <c r="H163" s="17" t="n">
@@ -5738,26 +5738,26 @@
       <c r="A164" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B164" s="9" t="n">
+      <c r="B164" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C164" s="10" t="inlineStr">
+      <c r="C164" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D164" s="10" t="inlineStr">
+      <c r="D164" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E164" s="11" t="n">
+      <c r="E164" s="10" t="n">
         <v>5284052.07</v>
       </c>
-      <c r="F164" s="8" t="n">
+      <c r="F164" s="11" t="n">
         <v>3296</v>
       </c>
-      <c r="G164" s="8" t="n">
+      <c r="G164" s="11" t="n">
         <v>3250</v>
       </c>
       <c r="H164" s="12" t="n">
@@ -5768,26 +5768,26 @@
       <c r="A165" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B165" s="14" t="n">
+      <c r="B165" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C165" s="15" t="inlineStr">
+      <c r="C165" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D165" s="15" t="inlineStr">
+      <c r="D165" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E165" s="16" t="n">
+      <c r="E165" s="15" t="n">
         <v>1787607.94</v>
       </c>
-      <c r="F165" s="13" t="n">
+      <c r="F165" s="16" t="n">
         <v>123</v>
       </c>
-      <c r="G165" s="13" t="n">
+      <c r="G165" s="16" t="n">
         <v>117</v>
       </c>
       <c r="H165" s="17" t="n">
@@ -5798,26 +5798,26 @@
       <c r="A166" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B166" s="9" t="n">
+      <c r="B166" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C166" s="10" t="inlineStr">
+      <c r="C166" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D166" s="10" t="inlineStr">
+      <c r="D166" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E166" s="11" t="n">
+      <c r="E166" s="10" t="n">
         <v>1122335.64</v>
       </c>
-      <c r="F166" s="8" t="n">
+      <c r="F166" s="11" t="n">
         <v>234</v>
       </c>
-      <c r="G166" s="8" t="n">
+      <c r="G166" s="11" t="n">
         <v>234</v>
       </c>
       <c r="H166" s="12" t="n">
@@ -5828,26 +5828,26 @@
       <c r="A167" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B167" s="14" t="n">
+      <c r="B167" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C167" s="15" t="inlineStr">
+      <c r="C167" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D167" s="15" t="inlineStr">
+      <c r="D167" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E167" s="16" t="n">
+      <c r="E167" s="15" t="n">
         <v>82271599.95999999</v>
       </c>
-      <c r="F167" s="13" t="n">
+      <c r="F167" s="16" t="n">
         <v>9657</v>
       </c>
-      <c r="G167" s="13" t="n">
+      <c r="G167" s="16" t="n">
         <v>9055</v>
       </c>
       <c r="H167" s="17" t="n">
@@ -5858,26 +5858,26 @@
       <c r="A168" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B168" s="9" t="n">
+      <c r="B168" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C168" s="10" t="inlineStr">
+      <c r="C168" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D168" s="10" t="inlineStr">
+      <c r="D168" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E168" s="11" t="n">
+      <c r="E168" s="10" t="n">
         <v>7599191.96</v>
       </c>
-      <c r="F168" s="8" t="n">
+      <c r="F168" s="11" t="n">
         <v>593</v>
       </c>
-      <c r="G168" s="8" t="n">
+      <c r="G168" s="11" t="n">
         <v>533</v>
       </c>
       <c r="H168" s="12" t="n">
@@ -5888,26 +5888,26 @@
       <c r="A169" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B169" s="14" t="n">
+      <c r="B169" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C169" s="15" t="inlineStr">
+      <c r="C169" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D169" s="15" t="inlineStr">
+      <c r="D169" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E169" s="16" t="n">
+      <c r="E169" s="15" t="n">
         <v>5700773.12</v>
       </c>
-      <c r="F169" s="13" t="n">
+      <c r="F169" s="16" t="n">
         <v>3376</v>
       </c>
-      <c r="G169" s="13" t="n">
+      <c r="G169" s="16" t="n">
         <v>3334</v>
       </c>
       <c r="H169" s="17" t="n">
@@ -5918,26 +5918,26 @@
       <c r="A170" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B170" s="9" t="n">
+      <c r="B170" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C170" s="10" t="inlineStr">
+      <c r="C170" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D170" s="10" t="inlineStr">
+      <c r="D170" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E170" s="11" t="n">
+      <c r="E170" s="10" t="n">
         <v>1828190.53</v>
       </c>
-      <c r="F170" s="8" t="n">
+      <c r="F170" s="11" t="n">
         <v>135</v>
       </c>
-      <c r="G170" s="8" t="n">
+      <c r="G170" s="11" t="n">
         <v>134</v>
       </c>
       <c r="H170" s="12" t="n">
@@ -5948,26 +5948,26 @@
       <c r="A171" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B171" s="14" t="n">
+      <c r="B171" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C171" s="15" t="inlineStr">
+      <c r="C171" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D171" s="15" t="inlineStr">
+      <c r="D171" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E171" s="16" t="n">
+      <c r="E171" s="15" t="n">
         <v>1116450.53</v>
       </c>
-      <c r="F171" s="13" t="n">
+      <c r="F171" s="16" t="n">
         <v>232</v>
       </c>
-      <c r="G171" s="13" t="n">
+      <c r="G171" s="16" t="n">
         <v>232</v>
       </c>
       <c r="H171" s="17" t="n">
@@ -5978,26 +5978,26 @@
       <c r="A172" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B172" s="9" t="n">
+      <c r="B172" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C172" s="10" t="inlineStr">
+      <c r="C172" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D172" s="10" t="inlineStr">
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E172" s="11" t="n">
+      <c r="E172" s="10" t="n">
         <v>140315998.57</v>
       </c>
-      <c r="F172" s="8" t="n">
+      <c r="F172" s="11" t="n">
         <v>18473</v>
       </c>
-      <c r="G172" s="8" t="n">
+      <c r="G172" s="11" t="n">
         <v>9039</v>
       </c>
       <c r="H172" s="12" t="n">
@@ -6008,26 +6008,26 @@
       <c r="A173" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B173" s="14" t="n">
+      <c r="B173" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C173" s="15" t="inlineStr">
+      <c r="C173" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D173" s="15" t="inlineStr">
+      <c r="D173" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E173" s="16" t="n">
+      <c r="E173" s="15" t="n">
         <v>13783971.56</v>
       </c>
-      <c r="F173" s="13" t="n">
+      <c r="F173" s="16" t="n">
         <v>1131</v>
       </c>
-      <c r="G173" s="13" t="n">
+      <c r="G173" s="16" t="n">
         <v>533</v>
       </c>
       <c r="H173" s="17" t="n">
@@ -6038,26 +6038,26 @@
       <c r="A174" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B174" s="9" t="n">
+      <c r="B174" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C174" s="10" t="inlineStr">
+      <c r="C174" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D174" s="10" t="inlineStr">
+      <c r="D174" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E174" s="11" t="n">
+      <c r="E174" s="10" t="n">
         <v>5818016.12</v>
       </c>
-      <c r="F174" s="8" t="n">
+      <c r="F174" s="11" t="n">
         <v>3411</v>
       </c>
-      <c r="G174" s="8" t="n">
+      <c r="G174" s="11" t="n">
         <v>3220</v>
       </c>
       <c r="H174" s="12" t="n">
@@ -6068,26 +6068,26 @@
       <c r="A175" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B175" s="14" t="n">
+      <c r="B175" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C175" s="15" t="inlineStr">
+      <c r="C175" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D175" s="15" t="inlineStr">
+      <c r="D175" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E175" s="16" t="n">
+      <c r="E175" s="15" t="n">
         <v>2972783.31</v>
       </c>
-      <c r="F175" s="13" t="n">
+      <c r="F175" s="16" t="n">
         <v>256</v>
       </c>
-      <c r="G175" s="13" t="n">
+      <c r="G175" s="16" t="n">
         <v>134</v>
       </c>
       <c r="H175" s="17" t="n">
@@ -6098,26 +6098,26 @@
       <c r="A176" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B176" s="9" t="n">
+      <c r="B176" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C176" s="10" t="inlineStr">
+      <c r="C176" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D176" s="10" t="inlineStr">
+      <c r="D176" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E176" s="11" t="n">
+      <c r="E176" s="10" t="n">
         <v>1951563.9</v>
       </c>
-      <c r="F176" s="8" t="n">
+      <c r="F176" s="11" t="n">
         <v>436</v>
       </c>
-      <c r="G176" s="8" t="n">
+      <c r="G176" s="11" t="n">
         <v>231</v>
       </c>
       <c r="H176" s="12" t="n">
@@ -6128,26 +6128,26 @@
       <c r="A177" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B177" s="14" t="n">
+      <c r="B177" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C177" s="15" t="inlineStr">
+      <c r="C177" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D177" s="15" t="inlineStr">
+      <c r="D177" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E177" s="16" t="n">
+      <c r="E177" s="15" t="n">
         <v>149284881.01</v>
       </c>
-      <c r="F177" s="13" t="n">
+      <c r="F177" s="16" t="n">
         <v>18912</v>
       </c>
-      <c r="G177" s="13" t="n">
+      <c r="G177" s="16" t="n">
         <v>9015</v>
       </c>
       <c r="H177" s="17" t="n">
@@ -6158,26 +6158,26 @@
       <c r="A178" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B178" s="9" t="n">
+      <c r="B178" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C178" s="10" t="inlineStr">
+      <c r="C178" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D178" s="10" t="inlineStr">
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E178" s="11" t="n">
+      <c r="E178" s="10" t="n">
         <v>14467348.99</v>
       </c>
-      <c r="F178" s="8" t="n">
+      <c r="F178" s="11" t="n">
         <v>1202</v>
       </c>
-      <c r="G178" s="8" t="n">
+      <c r="G178" s="11" t="n">
         <v>538</v>
       </c>
       <c r="H178" s="12" t="n">
@@ -6188,26 +6188,26 @@
       <c r="A179" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B179" s="14" t="n">
+      <c r="B179" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C179" s="15" t="inlineStr">
+      <c r="C179" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D179" s="15" t="inlineStr">
+      <c r="D179" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E179" s="16" t="n">
+      <c r="E179" s="15" t="n">
         <v>5901344.88</v>
       </c>
-      <c r="F179" s="13" t="n">
+      <c r="F179" s="16" t="n">
         <v>3244</v>
       </c>
-      <c r="G179" s="13" t="n">
+      <c r="G179" s="16" t="n">
         <v>3140</v>
       </c>
       <c r="H179" s="17" t="n">
@@ -6218,26 +6218,26 @@
       <c r="A180" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B180" s="9" t="n">
+      <c r="B180" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C180" s="10" t="inlineStr">
+      <c r="C180" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D180" s="10" t="inlineStr">
+      <c r="D180" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E180" s="11" t="n">
+      <c r="E180" s="10" t="n">
         <v>2869304.7</v>
       </c>
-      <c r="F180" s="8" t="n">
+      <c r="F180" s="11" t="n">
         <v>257</v>
       </c>
-      <c r="G180" s="8" t="n">
+      <c r="G180" s="11" t="n">
         <v>130</v>
       </c>
       <c r="H180" s="12" t="n">
@@ -6248,26 +6248,26 @@
       <c r="A181" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="B181" s="14" t="n">
+      <c r="B181" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C181" s="15" t="inlineStr">
+      <c r="C181" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D181" s="15" t="inlineStr">
+      <c r="D181" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E181" s="16" t="n">
+      <c r="E181" s="15" t="n">
         <v>2164432.86</v>
       </c>
-      <c r="F181" s="13" t="n">
+      <c r="F181" s="16" t="n">
         <v>429</v>
       </c>
-      <c r="G181" s="13" t="n">
+      <c r="G181" s="16" t="n">
         <v>228</v>
       </c>
       <c r="H181" s="17" t="n">
@@ -6278,26 +6278,26 @@
       <c r="A182" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B182" s="9" t="n">
+      <c r="B182" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C182" s="10" t="inlineStr">
+      <c r="C182" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D182" s="10" t="inlineStr">
+      <c r="D182" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E182" s="11" t="n">
+      <c r="E182" s="10" t="n">
         <v>91311379.18000001</v>
       </c>
-      <c r="F182" s="8" t="n">
+      <c r="F182" s="11" t="n">
         <v>13822</v>
       </c>
-      <c r="G182" s="8" t="n">
+      <c r="G182" s="11" t="n">
         <v>9000</v>
       </c>
       <c r="H182" s="12" t="n">
@@ -6308,26 +6308,26 @@
       <c r="A183" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B183" s="14" t="n">
+      <c r="B183" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C183" s="15" t="inlineStr">
+      <c r="C183" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D183" s="15" t="inlineStr">
+      <c r="D183" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E183" s="16" t="n">
+      <c r="E183" s="15" t="n">
         <v>7426327.51</v>
       </c>
-      <c r="F183" s="13" t="n">
+      <c r="F183" s="16" t="n">
         <v>601</v>
       </c>
-      <c r="G183" s="13" t="n">
+      <c r="G183" s="16" t="n">
         <v>534</v>
       </c>
       <c r="H183" s="17" t="n">
@@ -6338,26 +6338,26 @@
       <c r="A184" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B184" s="9" t="n">
+      <c r="B184" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C184" s="10" t="inlineStr">
+      <c r="C184" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D184" s="10" t="inlineStr">
+      <c r="D184" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E184" s="11" t="n">
+      <c r="E184" s="10" t="n">
         <v>3141972.89</v>
       </c>
-      <c r="F184" s="8" t="n">
+      <c r="F184" s="11" t="n">
         <v>2611</v>
       </c>
-      <c r="G184" s="8" t="n">
+      <c r="G184" s="11" t="n">
         <v>2588</v>
       </c>
       <c r="H184" s="12" t="n">
@@ -6368,26 +6368,26 @@
       <c r="A185" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B185" s="14" t="n">
+      <c r="B185" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C185" s="15" t="inlineStr">
+      <c r="C185" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D185" s="15" t="inlineStr">
+      <c r="D185" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E185" s="16" t="n">
+      <c r="E185" s="15" t="n">
         <v>1961355.51</v>
       </c>
-      <c r="F185" s="13" t="n">
+      <c r="F185" s="16" t="n">
         <v>136</v>
       </c>
-      <c r="G185" s="13" t="n">
+      <c r="G185" s="16" t="n">
         <v>135</v>
       </c>
       <c r="H185" s="17" t="n">
@@ -6398,26 +6398,26 @@
       <c r="A186" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B186" s="9" t="n">
+      <c r="B186" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C186" s="10" t="inlineStr">
+      <c r="C186" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D186" s="10" t="inlineStr">
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E186" s="11" t="n">
+      <c r="E186" s="10" t="n">
         <v>1075154.34</v>
       </c>
-      <c r="F186" s="8" t="n">
+      <c r="F186" s="11" t="n">
         <v>225</v>
       </c>
-      <c r="G186" s="8" t="n">
+      <c r="G186" s="11" t="n">
         <v>225</v>
       </c>
       <c r="H186" s="12" t="n">
@@ -6428,26 +6428,26 @@
       <c r="A187" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B187" s="14" t="n">
+      <c r="B187" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C187" s="15" t="inlineStr">
+      <c r="C187" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D187" s="15" t="inlineStr">
+      <c r="D187" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E187" s="16" t="n">
+      <c r="E187" s="15" t="n">
         <v>84482586.2</v>
       </c>
-      <c r="F187" s="13" t="n">
+      <c r="F187" s="16" t="n">
         <v>9756</v>
       </c>
-      <c r="G187" s="13" t="n">
+      <c r="G187" s="16" t="n">
         <v>9103</v>
       </c>
       <c r="H187" s="17" t="n">
@@ -6458,26 +6458,26 @@
       <c r="A188" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B188" s="9" t="n">
+      <c r="B188" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C188" s="10" t="inlineStr">
+      <c r="C188" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D188" s="10" t="inlineStr">
+      <c r="D188" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E188" s="11" t="n">
+      <c r="E188" s="10" t="n">
         <v>8240556.15</v>
       </c>
-      <c r="F188" s="8" t="n">
+      <c r="F188" s="11" t="n">
         <v>624</v>
       </c>
-      <c r="G188" s="8" t="n">
+      <c r="G188" s="11" t="n">
         <v>538</v>
       </c>
       <c r="H188" s="12" t="n">
@@ -6488,26 +6488,26 @@
       <c r="A189" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B189" s="14" t="n">
+      <c r="B189" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C189" s="15" t="inlineStr">
+      <c r="C189" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D189" s="15" t="inlineStr">
+      <c r="D189" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E189" s="16" t="n">
+      <c r="E189" s="15" t="n">
         <v>2437800.97</v>
       </c>
-      <c r="F189" s="13" t="n">
+      <c r="F189" s="16" t="n">
         <v>172</v>
       </c>
-      <c r="G189" s="13" t="n">
+      <c r="G189" s="16" t="n">
         <v>172</v>
       </c>
       <c r="H189" s="17" t="n">
@@ -6518,26 +6518,26 @@
       <c r="A190" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B190" s="9" t="n">
+      <c r="B190" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C190" s="10" t="inlineStr">
+      <c r="C190" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D190" s="10" t="inlineStr">
+      <c r="D190" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E190" s="11" t="n">
+      <c r="E190" s="10" t="n">
         <v>1121971.7</v>
       </c>
-      <c r="F190" s="8" t="n">
+      <c r="F190" s="11" t="n">
         <v>227</v>
       </c>
-      <c r="G190" s="8" t="n">
+      <c r="G190" s="11" t="n">
         <v>227</v>
       </c>
       <c r="H190" s="12" t="n">
@@ -6548,26 +6548,26 @@
       <c r="A191" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B191" s="14" t="n">
+      <c r="B191" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C191" s="15" t="inlineStr">
+      <c r="C191" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D191" s="15" t="inlineStr">
+      <c r="D191" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E191" s="16" t="n">
+      <c r="E191" s="15" t="n">
         <v>1111124.8</v>
       </c>
-      <c r="F191" s="13" t="n">
+      <c r="F191" s="16" t="n">
         <v>1060</v>
       </c>
-      <c r="G191" s="13" t="n">
+      <c r="G191" s="16" t="n">
         <v>1030</v>
       </c>
       <c r="H191" s="17" t="n">
@@ -6578,26 +6578,26 @@
       <c r="A192" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B192" s="9" t="n">
+      <c r="B192" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C192" s="10" t="inlineStr">
+      <c r="C192" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D192" s="10" t="inlineStr">
+      <c r="D192" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E192" s="11" t="n">
+      <c r="E192" s="10" t="n">
         <v>104417473.85</v>
       </c>
-      <c r="F192" s="8" t="n">
+      <c r="F192" s="11" t="n">
         <v>18772</v>
       </c>
-      <c r="G192" s="8" t="n">
+      <c r="G192" s="11" t="n">
         <v>9252</v>
       </c>
       <c r="H192" s="12" t="n">
@@ -6608,26 +6608,26 @@
       <c r="A193" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B193" s="14" t="n">
+      <c r="B193" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C193" s="15" t="inlineStr">
+      <c r="C193" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D193" s="15" t="inlineStr">
+      <c r="D193" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E193" s="16" t="n">
+      <c r="E193" s="15" t="n">
         <v>9221470.960000001</v>
       </c>
-      <c r="F193" s="13" t="n">
+      <c r="F193" s="16" t="n">
         <v>1169</v>
       </c>
-      <c r="G193" s="13" t="n">
+      <c r="G193" s="16" t="n">
         <v>552</v>
       </c>
       <c r="H193" s="17" t="n">
@@ -6638,26 +6638,26 @@
       <c r="A194" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B194" s="9" t="n">
+      <c r="B194" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C194" s="10" t="inlineStr">
+      <c r="C194" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D194" s="10" t="inlineStr">
+      <c r="D194" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E194" s="11" t="n">
+      <c r="E194" s="10" t="n">
         <v>4650725.38</v>
       </c>
-      <c r="F194" s="8" t="n">
+      <c r="F194" s="11" t="n">
         <v>3247</v>
       </c>
-      <c r="G194" s="8" t="n">
+      <c r="G194" s="11" t="n">
         <v>3217</v>
       </c>
       <c r="H194" s="12" t="n">
@@ -6668,26 +6668,26 @@
       <c r="A195" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B195" s="14" t="n">
+      <c r="B195" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C195" s="15" t="inlineStr">
+      <c r="C195" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D195" s="15" t="inlineStr">
+      <c r="D195" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E195" s="16" t="n">
+      <c r="E195" s="15" t="n">
         <v>2927687.4</v>
       </c>
-      <c r="F195" s="13" t="n">
+      <c r="F195" s="16" t="n">
         <v>314</v>
       </c>
-      <c r="G195" s="13" t="n">
+      <c r="G195" s="16" t="n">
         <v>176</v>
       </c>
       <c r="H195" s="17" t="n">
@@ -6698,26 +6698,26 @@
       <c r="A196" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B196" s="9" t="n">
+      <c r="B196" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C196" s="10" t="inlineStr">
+      <c r="C196" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D196" s="10" t="inlineStr">
+      <c r="D196" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E196" s="11" t="n">
+      <c r="E196" s="10" t="n">
         <v>1196757.42</v>
       </c>
-      <c r="F196" s="8" t="n">
+      <c r="F196" s="11" t="n">
         <v>419</v>
       </c>
-      <c r="G196" s="8" t="n">
+      <c r="G196" s="11" t="n">
         <v>223</v>
       </c>
       <c r="H196" s="12" t="n">
@@ -6728,26 +6728,26 @@
       <c r="A197" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B197" s="14" t="n">
+      <c r="B197" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C197" s="15" t="inlineStr">
+      <c r="C197" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D197" s="15" t="inlineStr">
+      <c r="D197" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E197" s="16" t="n">
+      <c r="E197" s="15" t="n">
         <v>89510033.20999999</v>
       </c>
-      <c r="F197" s="13" t="n">
+      <c r="F197" s="16" t="n">
         <v>10053</v>
       </c>
-      <c r="G197" s="13" t="n">
+      <c r="G197" s="16" t="n">
         <v>9210</v>
       </c>
       <c r="H197" s="17" t="n">
@@ -6758,26 +6758,26 @@
       <c r="A198" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B198" s="9" t="n">
+      <c r="B198" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C198" s="10" t="inlineStr">
+      <c r="C198" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D198" s="10" t="inlineStr">
+      <c r="D198" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E198" s="11" t="n">
+      <c r="E198" s="10" t="n">
         <v>8834549.859999999</v>
       </c>
-      <c r="F198" s="8" t="n">
+      <c r="F198" s="11" t="n">
         <v>650</v>
       </c>
-      <c r="G198" s="8" t="n">
+      <c r="G198" s="11" t="n">
         <v>559</v>
       </c>
       <c r="H198" s="12" t="n">
@@ -6788,26 +6788,26 @@
       <c r="A199" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B199" s="14" t="n">
+      <c r="B199" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C199" s="15" t="inlineStr">
+      <c r="C199" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D199" s="15" t="inlineStr">
+      <c r="D199" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E199" s="16" t="n">
+      <c r="E199" s="15" t="n">
         <v>4727095.74</v>
       </c>
-      <c r="F199" s="13" t="n">
+      <c r="F199" s="16" t="n">
         <v>2923</v>
       </c>
-      <c r="G199" s="13" t="n">
+      <c r="G199" s="16" t="n">
         <v>2882</v>
       </c>
       <c r="H199" s="17" t="n">
@@ -6818,26 +6818,26 @@
       <c r="A200" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B200" s="9" t="n">
+      <c r="B200" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C200" s="10" t="inlineStr">
+      <c r="C200" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D200" s="10" t="inlineStr">
+      <c r="D200" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E200" s="11" t="n">
+      <c r="E200" s="10" t="n">
         <v>2852026.07</v>
       </c>
-      <c r="F200" s="8" t="n">
+      <c r="F200" s="11" t="n">
         <v>187</v>
       </c>
-      <c r="G200" s="8" t="n">
+      <c r="G200" s="11" t="n">
         <v>174</v>
       </c>
       <c r="H200" s="12" t="n">
@@ -6848,26 +6848,26 @@
       <c r="A201" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B201" s="14" t="n">
+      <c r="B201" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C201" s="15" t="inlineStr">
+      <c r="C201" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D201" s="15" t="inlineStr">
+      <c r="D201" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E201" s="16" t="n">
+      <c r="E201" s="15" t="n">
         <v>1103402.18</v>
       </c>
-      <c r="F201" s="13" t="n">
+      <c r="F201" s="16" t="n">
         <v>223</v>
       </c>
-      <c r="G201" s="13" t="n">
+      <c r="G201" s="16" t="n">
         <v>223</v>
       </c>
       <c r="H201" s="17" t="n">
@@ -6878,26 +6878,26 @@
       <c r="A202" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B202" s="9" t="n">
+      <c r="B202" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C202" s="10" t="inlineStr">
+      <c r="C202" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D202" s="10" t="inlineStr">
+      <c r="D202" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E202" s="11" t="n">
+      <c r="E202" s="10" t="n">
         <v>90017395.12</v>
       </c>
-      <c r="F202" s="8" t="n">
+      <c r="F202" s="11" t="n">
         <v>10236</v>
       </c>
-      <c r="G202" s="8" t="n">
+      <c r="G202" s="11" t="n">
         <v>9341</v>
       </c>
       <c r="H202" s="12" t="n">
@@ -6908,26 +6908,26 @@
       <c r="A203" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B203" s="14" t="n">
+      <c r="B203" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C203" s="15" t="inlineStr">
+      <c r="C203" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D203" s="15" t="inlineStr">
+      <c r="D203" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E203" s="16" t="n">
+      <c r="E203" s="15" t="n">
         <v>8868592.01</v>
       </c>
-      <c r="F203" s="13" t="n">
+      <c r="F203" s="16" t="n">
         <v>696</v>
       </c>
-      <c r="G203" s="13" t="n">
+      <c r="G203" s="16" t="n">
         <v>557</v>
       </c>
       <c r="H203" s="17" t="n">
@@ -6938,26 +6938,26 @@
       <c r="A204" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B204" s="9" t="n">
+      <c r="B204" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C204" s="10" t="inlineStr">
+      <c r="C204" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D204" s="10" t="inlineStr">
+      <c r="D204" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E204" s="11" t="n">
+      <c r="E204" s="10" t="n">
         <v>5216809.72</v>
       </c>
-      <c r="F204" s="8" t="n">
+      <c r="F204" s="11" t="n">
         <v>3042</v>
       </c>
-      <c r="G204" s="8" t="n">
+      <c r="G204" s="11" t="n">
         <v>2962</v>
       </c>
       <c r="H204" s="12" t="n">
@@ -6968,26 +6968,26 @@
       <c r="A205" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B205" s="14" t="n">
+      <c r="B205" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C205" s="15" t="inlineStr">
+      <c r="C205" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D205" s="15" t="inlineStr">
+      <c r="D205" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E205" s="16" t="n">
+      <c r="E205" s="15" t="n">
         <v>2824061.96</v>
       </c>
-      <c r="F205" s="13" t="n">
+      <c r="F205" s="16" t="n">
         <v>188</v>
       </c>
-      <c r="G205" s="13" t="n">
+      <c r="G205" s="16" t="n">
         <v>174</v>
       </c>
       <c r="H205" s="17" t="n">
@@ -6998,26 +6998,26 @@
       <c r="A206" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B206" s="9" t="n">
+      <c r="B206" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C206" s="10" t="inlineStr">
+      <c r="C206" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D206" s="10" t="inlineStr">
+      <c r="D206" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E206" s="11" t="n">
+      <c r="E206" s="10" t="n">
         <v>1100378.67</v>
       </c>
-      <c r="F206" s="8" t="n">
+      <c r="F206" s="11" t="n">
         <v>217</v>
       </c>
-      <c r="G206" s="8" t="n">
+      <c r="G206" s="11" t="n">
         <v>217</v>
       </c>
       <c r="H206" s="12" t="n">
@@ -7028,26 +7028,26 @@
       <c r="A207" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B207" s="14" t="n">
+      <c r="B207" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C207" s="15" t="inlineStr">
+      <c r="C207" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D207" s="15" t="inlineStr">
+      <c r="D207" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E207" s="16" t="n">
+      <c r="E207" s="15" t="n">
         <v>93664028.06</v>
       </c>
-      <c r="F207" s="13" t="n">
+      <c r="F207" s="16" t="n">
         <v>10063</v>
       </c>
-      <c r="G207" s="13" t="n">
+      <c r="G207" s="16" t="n">
         <v>9322</v>
       </c>
       <c r="H207" s="17" t="n">
@@ -7058,26 +7058,26 @@
       <c r="A208" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B208" s="9" t="n">
+      <c r="B208" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C208" s="10" t="inlineStr">
+      <c r="C208" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D208" s="10" t="inlineStr">
+      <c r="D208" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E208" s="11" t="n">
+      <c r="E208" s="10" t="n">
         <v>9125136.529999999</v>
       </c>
-      <c r="F208" s="8" t="n">
+      <c r="F208" s="11" t="n">
         <v>643</v>
       </c>
-      <c r="G208" s="8" t="n">
+      <c r="G208" s="11" t="n">
         <v>560</v>
       </c>
       <c r="H208" s="12" t="n">
@@ -7088,26 +7088,26 @@
       <c r="A209" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B209" s="14" t="n">
+      <c r="B209" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C209" s="15" t="inlineStr">
+      <c r="C209" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D209" s="15" t="inlineStr">
+      <c r="D209" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E209" s="16" t="n">
+      <c r="E209" s="15" t="n">
         <v>5709673.12</v>
       </c>
-      <c r="F209" s="13" t="n">
+      <c r="F209" s="16" t="n">
         <v>3175</v>
       </c>
-      <c r="G209" s="13" t="n">
+      <c r="G209" s="16" t="n">
         <v>3102</v>
       </c>
       <c r="H209" s="17" t="n">
@@ -7118,26 +7118,26 @@
       <c r="A210" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B210" s="9" t="n">
+      <c r="B210" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C210" s="10" t="inlineStr">
+      <c r="C210" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D210" s="10" t="inlineStr">
+      <c r="D210" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E210" s="11" t="n">
+      <c r="E210" s="10" t="n">
         <v>2908912.37</v>
       </c>
-      <c r="F210" s="8" t="n">
+      <c r="F210" s="11" t="n">
         <v>177</v>
       </c>
-      <c r="G210" s="8" t="n">
+      <c r="G210" s="11" t="n">
         <v>173</v>
       </c>
       <c r="H210" s="12" t="n">
@@ -7148,26 +7148,26 @@
       <c r="A211" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B211" s="14" t="n">
+      <c r="B211" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C211" s="15" t="inlineStr">
+      <c r="C211" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D211" s="15" t="inlineStr">
+      <c r="D211" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E211" s="16" t="n">
+      <c r="E211" s="15" t="n">
         <v>1106489.67</v>
       </c>
-      <c r="F211" s="13" t="n">
+      <c r="F211" s="16" t="n">
         <v>214</v>
       </c>
-      <c r="G211" s="13" t="n">
+      <c r="G211" s="16" t="n">
         <v>214</v>
       </c>
       <c r="H211" s="17" t="n">
@@ -7178,26 +7178,26 @@
       <c r="A212" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B212" s="9" t="n">
+      <c r="B212" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C212" s="10" t="inlineStr">
+      <c r="C212" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D212" s="10" t="inlineStr">
+      <c r="D212" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E212" s="11" t="n">
+      <c r="E212" s="10" t="n">
         <v>93308814</v>
       </c>
-      <c r="F212" s="8" t="n">
+      <c r="F212" s="11" t="n">
         <v>10570</v>
       </c>
-      <c r="G212" s="8" t="n">
+      <c r="G212" s="11" t="n">
         <v>9349</v>
       </c>
       <c r="H212" s="12" t="n">
@@ -7208,26 +7208,26 @@
       <c r="A213" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B213" s="14" t="n">
+      <c r="B213" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C213" s="15" t="inlineStr">
+      <c r="C213" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D213" s="15" t="inlineStr">
+      <c r="D213" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E213" s="16" t="n">
+      <c r="E213" s="15" t="n">
         <v>9625690.68</v>
       </c>
-      <c r="F213" s="13" t="n">
+      <c r="F213" s="16" t="n">
         <v>721</v>
       </c>
-      <c r="G213" s="13" t="n">
+      <c r="G213" s="16" t="n">
         <v>562</v>
       </c>
       <c r="H213" s="17" t="n">
@@ -7238,26 +7238,26 @@
       <c r="A214" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B214" s="9" t="n">
+      <c r="B214" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C214" s="10" t="inlineStr">
+      <c r="C214" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D214" s="10" t="inlineStr">
+      <c r="D214" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E214" s="11" t="n">
+      <c r="E214" s="10" t="n">
         <v>5548903.17</v>
       </c>
-      <c r="F214" s="8" t="n">
+      <c r="F214" s="11" t="n">
         <v>3133</v>
       </c>
-      <c r="G214" s="8" t="n">
+      <c r="G214" s="11" t="n">
         <v>3105</v>
       </c>
       <c r="H214" s="12" t="n">
@@ -7268,26 +7268,26 @@
       <c r="A215" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B215" s="14" t="n">
+      <c r="B215" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C215" s="15" t="inlineStr">
+      <c r="C215" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D215" s="15" t="inlineStr">
+      <c r="D215" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E215" s="16" t="n">
+      <c r="E215" s="15" t="n">
         <v>2930484.77</v>
       </c>
-      <c r="F215" s="13" t="n">
+      <c r="F215" s="16" t="n">
         <v>184</v>
       </c>
-      <c r="G215" s="13" t="n">
+      <c r="G215" s="16" t="n">
         <v>175</v>
       </c>
       <c r="H215" s="17" t="n">
@@ -7298,26 +7298,26 @@
       <c r="A216" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B216" s="9" t="n">
+      <c r="B216" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C216" s="10" t="inlineStr">
+      <c r="C216" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D216" s="10" t="inlineStr">
+      <c r="D216" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E216" s="11" t="n">
+      <c r="E216" s="10" t="n">
         <v>1108889.7</v>
       </c>
-      <c r="F216" s="8" t="n">
+      <c r="F216" s="11" t="n">
         <v>214</v>
       </c>
-      <c r="G216" s="8" t="n">
+      <c r="G216" s="11" t="n">
         <v>214</v>
       </c>
       <c r="H216" s="12" t="n">
@@ -7328,26 +7328,26 @@
       <c r="A217" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B217" s="14" t="n">
+      <c r="B217" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C217" s="15" t="inlineStr">
+      <c r="C217" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D217" s="15" t="inlineStr">
+      <c r="D217" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E217" s="16" t="n">
+      <c r="E217" s="15" t="n">
         <v>93401788.26000001</v>
       </c>
-      <c r="F217" s="13" t="n">
+      <c r="F217" s="16" t="n">
         <v>10052</v>
       </c>
-      <c r="G217" s="13" t="n">
+      <c r="G217" s="16" t="n">
         <v>9354</v>
       </c>
       <c r="H217" s="17" t="n">
@@ -7358,26 +7358,26 @@
       <c r="A218" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B218" s="9" t="n">
+      <c r="B218" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C218" s="10" t="inlineStr">
+      <c r="C218" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D218" s="10" t="inlineStr">
+      <c r="D218" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E218" s="11" t="n">
+      <c r="E218" s="10" t="n">
         <v>9267680.949999999</v>
       </c>
-      <c r="F218" s="8" t="n">
+      <c r="F218" s="11" t="n">
         <v>643</v>
       </c>
-      <c r="G218" s="8" t="n">
+      <c r="G218" s="11" t="n">
         <v>560</v>
       </c>
       <c r="H218" s="12" t="n">
@@ -7388,26 +7388,26 @@
       <c r="A219" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B219" s="14" t="n">
+      <c r="B219" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C219" s="15" t="inlineStr">
+      <c r="C219" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D219" s="15" t="inlineStr">
+      <c r="D219" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E219" s="16" t="n">
+      <c r="E219" s="15" t="n">
         <v>3869336.4</v>
       </c>
-      <c r="F219" s="13" t="n">
+      <c r="F219" s="16" t="n">
         <v>2795</v>
       </c>
-      <c r="G219" s="13" t="n">
+      <c r="G219" s="16" t="n">
         <v>2763</v>
       </c>
       <c r="H219" s="17" t="n">
@@ -7418,26 +7418,26 @@
       <c r="A220" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B220" s="9" t="n">
+      <c r="B220" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C220" s="10" t="inlineStr">
+      <c r="C220" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D220" s="10" t="inlineStr">
+      <c r="D220" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E220" s="11" t="n">
+      <c r="E220" s="10" t="n">
         <v>2822436.43</v>
       </c>
-      <c r="F220" s="8" t="n">
+      <c r="F220" s="11" t="n">
         <v>179</v>
       </c>
-      <c r="G220" s="8" t="n">
+      <c r="G220" s="11" t="n">
         <v>173</v>
       </c>
       <c r="H220" s="12" t="n">
@@ -7448,26 +7448,26 @@
       <c r="A221" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B221" s="14" t="n">
+      <c r="B221" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C221" s="15" t="inlineStr">
+      <c r="C221" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D221" s="15" t="inlineStr">
+      <c r="D221" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E221" s="16" t="n">
+      <c r="E221" s="15" t="n">
         <v>1102157.2</v>
       </c>
-      <c r="F221" s="13" t="n">
+      <c r="F221" s="16" t="n">
         <v>212</v>
       </c>
-      <c r="G221" s="13" t="n">
+      <c r="G221" s="16" t="n">
         <v>212</v>
       </c>
       <c r="H221" s="17" t="n">
@@ -7478,26 +7478,26 @@
       <c r="A222" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B222" s="9" t="n">
+      <c r="B222" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C222" s="10" t="inlineStr">
+      <c r="C222" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D222" s="10" t="inlineStr">
+      <c r="D222" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E222" s="11" t="n">
+      <c r="E222" s="10" t="n">
         <v>92666824.66</v>
       </c>
-      <c r="F222" s="8" t="n">
+      <c r="F222" s="11" t="n">
         <v>10364</v>
       </c>
-      <c r="G222" s="8" t="n">
+      <c r="G222" s="11" t="n">
         <v>9344</v>
       </c>
       <c r="H222" s="12" t="n">
@@ -7508,26 +7508,26 @@
       <c r="A223" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B223" s="14" t="n">
+      <c r="B223" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C223" s="15" t="inlineStr">
+      <c r="C223" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D223" s="15" t="inlineStr">
+      <c r="D223" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E223" s="16" t="n">
+      <c r="E223" s="15" t="n">
         <v>9015270.050000001</v>
       </c>
-      <c r="F223" s="13" t="n">
+      <c r="F223" s="16" t="n">
         <v>646</v>
       </c>
-      <c r="G223" s="13" t="n">
+      <c r="G223" s="16" t="n">
         <v>559</v>
       </c>
       <c r="H223" s="17" t="n">
@@ -7538,26 +7538,26 @@
       <c r="A224" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B224" s="9" t="n">
+      <c r="B224" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C224" s="10" t="inlineStr">
+      <c r="C224" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D224" s="10" t="inlineStr">
+      <c r="D224" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E224" s="11" t="n">
+      <c r="E224" s="10" t="n">
         <v>6045972.7</v>
       </c>
-      <c r="F224" s="8" t="n">
+      <c r="F224" s="11" t="n">
         <v>3312</v>
       </c>
-      <c r="G224" s="8" t="n">
+      <c r="G224" s="11" t="n">
         <v>3273</v>
       </c>
       <c r="H224" s="12" t="n">
@@ -7568,26 +7568,26 @@
       <c r="A225" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B225" s="14" t="n">
+      <c r="B225" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C225" s="15" t="inlineStr">
+      <c r="C225" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D225" s="15" t="inlineStr">
+      <c r="D225" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E225" s="16" t="n">
+      <c r="E225" s="15" t="n">
         <v>2911899.4</v>
       </c>
-      <c r="F225" s="13" t="n">
+      <c r="F225" s="16" t="n">
         <v>179</v>
       </c>
-      <c r="G225" s="13" t="n">
+      <c r="G225" s="16" t="n">
         <v>174</v>
       </c>
       <c r="H225" s="17" t="n">
@@ -7598,26 +7598,26 @@
       <c r="A226" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B226" s="9" t="n">
+      <c r="B226" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C226" s="10" t="inlineStr">
+      <c r="C226" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D226" s="10" t="inlineStr">
+      <c r="D226" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E226" s="11" t="n">
+      <c r="E226" s="10" t="n">
         <v>1094068.51</v>
       </c>
-      <c r="F226" s="8" t="n">
+      <c r="F226" s="11" t="n">
         <v>190</v>
       </c>
-      <c r="G226" s="8" t="n">
+      <c r="G226" s="11" t="n">
         <v>190</v>
       </c>
       <c r="H226" s="12" t="n">
@@ -7628,26 +7628,26 @@
       <c r="A227" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B227" s="14" t="n">
+      <c r="B227" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C227" s="15" t="inlineStr">
+      <c r="C227" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D227" s="15" t="inlineStr">
+      <c r="D227" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E227" s="16" t="n">
+      <c r="E227" s="15" t="n">
         <v>90625038.63</v>
       </c>
-      <c r="F227" s="13" t="n">
+      <c r="F227" s="16" t="n">
         <v>10019</v>
       </c>
-      <c r="G227" s="13" t="n">
+      <c r="G227" s="16" t="n">
         <v>9309</v>
       </c>
       <c r="H227" s="17" t="n">
@@ -7658,26 +7658,26 @@
       <c r="A228" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B228" s="9" t="n">
+      <c r="B228" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C228" s="10" t="inlineStr">
+      <c r="C228" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D228" s="10" t="inlineStr">
+      <c r="D228" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E228" s="11" t="n">
+      <c r="E228" s="10" t="n">
         <v>8874144.539999999</v>
       </c>
-      <c r="F228" s="8" t="n">
+      <c r="F228" s="11" t="n">
         <v>631</v>
       </c>
-      <c r="G228" s="8" t="n">
+      <c r="G228" s="11" t="n">
         <v>558</v>
       </c>
       <c r="H228" s="12" t="n">
@@ -7688,26 +7688,26 @@
       <c r="A229" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B229" s="14" t="n">
+      <c r="B229" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C229" s="15" t="inlineStr">
+      <c r="C229" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D229" s="15" t="inlineStr">
+      <c r="D229" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E229" s="16" t="n">
+      <c r="E229" s="15" t="n">
         <v>6688658.75</v>
       </c>
-      <c r="F229" s="13" t="n">
+      <c r="F229" s="16" t="n">
         <v>3444</v>
       </c>
-      <c r="G229" s="13" t="n">
+      <c r="G229" s="16" t="n">
         <v>3423</v>
       </c>
       <c r="H229" s="17" t="n">
@@ -7718,26 +7718,26 @@
       <c r="A230" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B230" s="9" t="n">
+      <c r="B230" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="C230" s="10" t="inlineStr">
+      <c r="C230" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D230" s="10" t="inlineStr">
+      <c r="D230" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E230" s="11" t="n">
+      <c r="E230" s="10" t="n">
         <v>3003705.62</v>
       </c>
-      <c r="F230" s="8" t="n">
+      <c r="F230" s="11" t="n">
         <v>181</v>
       </c>
-      <c r="G230" s="8" t="n">
+      <c r="G230" s="11" t="n">
         <v>176</v>
       </c>
       <c r="H230" s="12" t="n">
@@ -7748,26 +7748,26 @@
       <c r="A231" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B231" s="14" t="n">
+      <c r="B231" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C231" s="15" t="inlineStr">
+      <c r="C231" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D231" s="15" t="inlineStr">
+      <c r="D231" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E231" s="16" t="n">
+      <c r="E231" s="15" t="n">
         <v>1088006.94</v>
       </c>
-      <c r="F231" s="13" t="n">
+      <c r="F231" s="16" t="n">
         <v>188</v>
       </c>
-      <c r="G231" s="13" t="n">
+      <c r="G231" s="16" t="n">
         <v>188</v>
       </c>
       <c r="H231" s="17" t="n">
@@ -7778,26 +7778,26 @@
       <c r="A232" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B232" s="9" t="n">
+      <c r="B232" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C232" s="10" t="inlineStr">
+      <c r="C232" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D232" s="10" t="inlineStr">
+      <c r="D232" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E232" s="11" t="n">
+      <c r="E232" s="10" t="n">
         <v>122469667.84</v>
       </c>
-      <c r="F232" s="8" t="n">
+      <c r="F232" s="11" t="n">
         <v>10072</v>
       </c>
-      <c r="G232" s="8" t="n">
+      <c r="G232" s="11" t="n">
         <v>9271</v>
       </c>
       <c r="H232" s="12" t="n">
@@ -7808,26 +7808,26 @@
       <c r="A233" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B233" s="14" t="n">
+      <c r="B233" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C233" s="15" t="inlineStr">
+      <c r="C233" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D233" s="15" t="inlineStr">
+      <c r="D233" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E233" s="16" t="n">
+      <c r="E233" s="15" t="n">
         <v>12370694.61</v>
       </c>
-      <c r="F233" s="13" t="n">
+      <c r="F233" s="16" t="n">
         <v>643</v>
       </c>
-      <c r="G233" s="13" t="n">
+      <c r="G233" s="16" t="n">
         <v>564</v>
       </c>
       <c r="H233" s="17" t="n">
@@ -7838,26 +7838,26 @@
       <c r="A234" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B234" s="9" t="n">
+      <c r="B234" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C234" s="10" t="inlineStr">
+      <c r="C234" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D234" s="10" t="inlineStr">
+      <c r="D234" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E234" s="11" t="n">
+      <c r="E234" s="10" t="n">
         <v>6667514.76</v>
       </c>
-      <c r="F234" s="8" t="n">
+      <c r="F234" s="11" t="n">
         <v>3393</v>
       </c>
-      <c r="G234" s="8" t="n">
+      <c r="G234" s="11" t="n">
         <v>3347</v>
       </c>
       <c r="H234" s="12" t="n">
@@ -7868,26 +7868,26 @@
       <c r="A235" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B235" s="14" t="n">
+      <c r="B235" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C235" s="15" t="inlineStr">
+      <c r="C235" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D235" s="15" t="inlineStr">
+      <c r="D235" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E235" s="16" t="n">
+      <c r="E235" s="15" t="n">
         <v>4232671.24</v>
       </c>
-      <c r="F235" s="13" t="n">
+      <c r="F235" s="16" t="n">
         <v>191</v>
       </c>
-      <c r="G235" s="13" t="n">
+      <c r="G235" s="16" t="n">
         <v>175</v>
       </c>
       <c r="H235" s="17" t="n">
@@ -7898,26 +7898,26 @@
       <c r="A236" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B236" s="9" t="n">
+      <c r="B236" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C236" s="10" t="inlineStr">
+      <c r="C236" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D236" s="10" t="inlineStr">
+      <c r="D236" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E236" s="11" t="n">
+      <c r="E236" s="10" t="n">
         <v>1614531.69</v>
       </c>
-      <c r="F236" s="8" t="n">
+      <c r="F236" s="11" t="n">
         <v>189</v>
       </c>
-      <c r="G236" s="8" t="n">
+      <c r="G236" s="11" t="n">
         <v>189</v>
       </c>
       <c r="H236" s="12" t="n">
@@ -7928,26 +7928,26 @@
       <c r="A237" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B237" s="14" t="n">
+      <c r="B237" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C237" s="15" t="inlineStr">
+      <c r="C237" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D237" s="15" t="inlineStr">
+      <c r="D237" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E237" s="16" t="n">
+      <c r="E237" s="15" t="n">
         <v>165334593.45</v>
       </c>
-      <c r="F237" s="13" t="n">
+      <c r="F237" s="16" t="n">
         <v>19194</v>
       </c>
-      <c r="G237" s="13" t="n">
+      <c r="G237" s="16" t="n">
         <v>9257</v>
       </c>
       <c r="H237" s="17" t="n">
@@ -7958,26 +7958,26 @@
       <c r="A238" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B238" s="9" t="n">
+      <c r="B238" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C238" s="10" t="inlineStr">
+      <c r="C238" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D238" s="10" t="inlineStr">
+      <c r="D238" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E238" s="11" t="n">
+      <c r="E238" s="10" t="n">
         <v>16348302.5</v>
       </c>
-      <c r="F238" s="8" t="n">
+      <c r="F238" s="11" t="n">
         <v>1227</v>
       </c>
-      <c r="G238" s="8" t="n">
+      <c r="G238" s="11" t="n">
         <v>564</v>
       </c>
       <c r="H238" s="12" t="n">
@@ -7988,26 +7988,26 @@
       <c r="A239" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B239" s="14" t="n">
+      <c r="B239" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C239" s="15" t="inlineStr">
+      <c r="C239" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D239" s="15" t="inlineStr">
+      <c r="D239" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E239" s="16" t="n">
+      <c r="E239" s="15" t="n">
         <v>6571871.9</v>
       </c>
-      <c r="F239" s="13" t="n">
+      <c r="F239" s="16" t="n">
         <v>3476</v>
       </c>
-      <c r="G239" s="13" t="n">
+      <c r="G239" s="16" t="n">
         <v>3294</v>
       </c>
       <c r="H239" s="17" t="n">
@@ -8018,26 +8018,26 @@
       <c r="A240" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B240" s="9" t="n">
+      <c r="B240" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C240" s="10" t="inlineStr">
+      <c r="C240" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D240" s="10" t="inlineStr">
+      <c r="D240" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E240" s="11" t="n">
+      <c r="E240" s="10" t="n">
         <v>5187789.88</v>
       </c>
-      <c r="F240" s="8" t="n">
+      <c r="F240" s="11" t="n">
         <v>353</v>
       </c>
-      <c r="G240" s="8" t="n">
+      <c r="G240" s="11" t="n">
         <v>171</v>
       </c>
       <c r="H240" s="12" t="n">
@@ -8048,26 +8048,26 @@
       <c r="A241" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="B241" s="14" t="n">
+      <c r="B241" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C241" s="15" t="inlineStr">
+      <c r="C241" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D241" s="15" t="inlineStr">
+      <c r="D241" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E241" s="16" t="n">
+      <c r="E241" s="15" t="n">
         <v>2176084.26</v>
       </c>
-      <c r="F241" s="13" t="n">
+      <c r="F241" s="16" t="n">
         <v>376</v>
       </c>
-      <c r="G241" s="13" t="n">
+      <c r="G241" s="16" t="n">
         <v>188</v>
       </c>
       <c r="H241" s="17" t="n">
@@ -8078,26 +8078,26 @@
       <c r="A242" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B242" s="9" t="n">
+      <c r="B242" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C242" s="10" t="inlineStr">
+      <c r="C242" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D242" s="10" t="inlineStr">
+      <c r="D242" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E242" s="11" t="n">
+      <c r="E242" s="10" t="n">
         <v>102124675.23</v>
       </c>
-      <c r="F242" s="8" t="n">
+      <c r="F242" s="11" t="n">
         <v>14047</v>
       </c>
-      <c r="G242" s="8" t="n">
+      <c r="G242" s="11" t="n">
         <v>9167</v>
       </c>
       <c r="H242" s="12" t="n">
@@ -8108,26 +8108,26 @@
       <c r="A243" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B243" s="14" t="n">
+      <c r="B243" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C243" s="15" t="inlineStr">
+      <c r="C243" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D243" s="15" t="inlineStr">
+      <c r="D243" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E243" s="16" t="n">
+      <c r="E243" s="15" t="n">
         <v>9020714.800000001</v>
       </c>
-      <c r="F243" s="13" t="n">
+      <c r="F243" s="16" t="n">
         <v>666</v>
       </c>
-      <c r="G243" s="13" t="n">
+      <c r="G243" s="16" t="n">
         <v>564</v>
       </c>
       <c r="H243" s="17" t="n">
@@ -8138,26 +8138,26 @@
       <c r="A244" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B244" s="9" t="n">
+      <c r="B244" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C244" s="10" t="inlineStr">
+      <c r="C244" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D244" s="10" t="inlineStr">
+      <c r="D244" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E244" s="11" t="n">
+      <c r="E244" s="10" t="n">
         <v>4153904.73</v>
       </c>
-      <c r="F244" s="8" t="n">
+      <c r="F244" s="11" t="n">
         <v>2854</v>
       </c>
-      <c r="G244" s="8" t="n">
+      <c r="G244" s="11" t="n">
         <v>2836</v>
       </c>
       <c r="H244" s="12" t="n">
@@ -8168,26 +8168,26 @@
       <c r="A245" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B245" s="14" t="n">
+      <c r="B245" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C245" s="15" t="inlineStr">
+      <c r="C245" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D245" s="15" t="inlineStr">
+      <c r="D245" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E245" s="16" t="n">
+      <c r="E245" s="15" t="n">
         <v>3204051.46</v>
       </c>
-      <c r="F245" s="13" t="n">
+      <c r="F245" s="16" t="n">
         <v>188</v>
       </c>
-      <c r="G245" s="13" t="n">
+      <c r="G245" s="16" t="n">
         <v>173</v>
       </c>
       <c r="H245" s="17" t="n">
@@ -8198,26 +8198,26 @@
       <c r="A246" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B246" s="9" t="n">
+      <c r="B246" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C246" s="10" t="inlineStr">
+      <c r="C246" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D246" s="10" t="inlineStr">
+      <c r="D246" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E246" s="11" t="n">
+      <c r="E246" s="10" t="n">
         <v>1098289.23</v>
       </c>
-      <c r="F246" s="8" t="n">
+      <c r="F246" s="11" t="n">
         <v>188</v>
       </c>
-      <c r="G246" s="8" t="n">
+      <c r="G246" s="11" t="n">
         <v>188</v>
       </c>
       <c r="H246" s="12" t="n">
@@ -8228,26 +8228,26 @@
       <c r="A247" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B247" s="14" t="n">
+      <c r="B247" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C247" s="15" t="inlineStr">
+      <c r="C247" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D247" s="15" t="inlineStr">
+      <c r="D247" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E247" s="16" t="n">
+      <c r="E247" s="15" t="n">
         <v>88678656.13</v>
       </c>
-      <c r="F247" s="13" t="n">
+      <c r="F247" s="16" t="n">
         <v>9898</v>
       </c>
-      <c r="G247" s="13" t="n">
+      <c r="G247" s="16" t="n">
         <v>9147</v>
       </c>
       <c r="H247" s="17" t="n">
@@ -8258,26 +8258,26 @@
       <c r="A248" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B248" s="9" t="n">
+      <c r="B248" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C248" s="10" t="inlineStr">
+      <c r="C248" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D248" s="10" t="inlineStr">
+      <c r="D248" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E248" s="11" t="n">
+      <c r="E248" s="10" t="n">
         <v>9387958.16</v>
       </c>
-      <c r="F248" s="8" t="n">
+      <c r="F248" s="11" t="n">
         <v>668</v>
       </c>
-      <c r="G248" s="8" t="n">
+      <c r="G248" s="11" t="n">
         <v>564</v>
       </c>
       <c r="H248" s="12" t="n">
@@ -8288,26 +8288,26 @@
       <c r="A249" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B249" s="14" t="n">
+      <c r="B249" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C249" s="15" t="inlineStr">
+      <c r="C249" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D249" s="15" t="inlineStr">
+      <c r="D249" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E249" s="16" t="n">
+      <c r="E249" s="15" t="n">
         <v>3236545.28</v>
       </c>
-      <c r="F249" s="13" t="n">
+      <c r="F249" s="16" t="n">
         <v>198</v>
       </c>
-      <c r="G249" s="13" t="n">
+      <c r="G249" s="16" t="n">
         <v>183</v>
       </c>
       <c r="H249" s="17" t="n">
@@ -8318,26 +8318,26 @@
       <c r="A250" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B250" s="9" t="n">
+      <c r="B250" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C250" s="10" t="inlineStr">
+      <c r="C250" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D250" s="10" t="inlineStr">
+      <c r="D250" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E250" s="11" t="n">
+      <c r="E250" s="10" t="n">
         <v>1217749.71</v>
       </c>
-      <c r="F250" s="8" t="n">
+      <c r="F250" s="11" t="n">
         <v>899</v>
       </c>
-      <c r="G250" s="8" t="n">
+      <c r="G250" s="11" t="n">
         <v>819</v>
       </c>
       <c r="H250" s="12" t="n">
@@ -8348,26 +8348,26 @@
       <c r="A251" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B251" s="14" t="n">
+      <c r="B251" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C251" s="15" t="inlineStr">
+      <c r="C251" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D251" s="15" t="inlineStr">
+      <c r="D251" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E251" s="16" t="n">
+      <c r="E251" s="15" t="n">
         <v>1086874.99</v>
       </c>
-      <c r="F251" s="13" t="n">
+      <c r="F251" s="16" t="n">
         <v>187</v>
       </c>
-      <c r="G251" s="13" t="n">
+      <c r="G251" s="16" t="n">
         <v>187</v>
       </c>
       <c r="H251" s="17" t="n">
@@ -8378,26 +8378,26 @@
       <c r="A252" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B252" s="9" t="n">
+      <c r="B252" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C252" s="10" t="inlineStr">
+      <c r="C252" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D252" s="10" t="inlineStr">
+      <c r="D252" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E252" s="11" t="n">
+      <c r="E252" s="10" t="n">
         <v>111408031.77</v>
       </c>
-      <c r="F252" s="8" t="n">
+      <c r="F252" s="11" t="n">
         <v>10126</v>
       </c>
-      <c r="G252" s="8" t="n">
+      <c r="G252" s="11" t="n">
         <v>9330</v>
       </c>
       <c r="H252" s="12" t="n">
@@ -8408,26 +8408,26 @@
       <c r="A253" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B253" s="14" t="n">
+      <c r="B253" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C253" s="15" t="inlineStr">
+      <c r="C253" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D253" s="15" t="inlineStr">
+      <c r="D253" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E253" s="16" t="n">
+      <c r="E253" s="15" t="n">
         <v>9932620.92</v>
       </c>
-      <c r="F253" s="13" t="n">
+      <c r="F253" s="16" t="n">
         <v>641</v>
       </c>
-      <c r="G253" s="13" t="n">
+      <c r="G253" s="16" t="n">
         <v>556</v>
       </c>
       <c r="H253" s="17" t="n">
@@ -8438,26 +8438,26 @@
       <c r="A254" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B254" s="9" t="n">
+      <c r="B254" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C254" s="10" t="inlineStr">
+      <c r="C254" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D254" s="10" t="inlineStr">
+      <c r="D254" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E254" s="11" t="n">
+      <c r="E254" s="10" t="n">
         <v>4771985.94</v>
       </c>
-      <c r="F254" s="8" t="n">
+      <c r="F254" s="11" t="n">
         <v>3358</v>
       </c>
-      <c r="G254" s="8" t="n">
+      <c r="G254" s="11" t="n">
         <v>3337</v>
       </c>
       <c r="H254" s="12" t="n">
@@ -8468,26 +8468,26 @@
       <c r="A255" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B255" s="14" t="n">
+      <c r="B255" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C255" s="15" t="inlineStr">
+      <c r="C255" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D255" s="15" t="inlineStr">
+      <c r="D255" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E255" s="16" t="n">
+      <c r="E255" s="15" t="n">
         <v>3013807.07</v>
       </c>
-      <c r="F255" s="13" t="n">
+      <c r="F255" s="16" t="n">
         <v>179</v>
       </c>
-      <c r="G255" s="13" t="n">
+      <c r="G255" s="16" t="n">
         <v>159</v>
       </c>
       <c r="H255" s="17" t="n">
@@ -8498,26 +8498,26 @@
       <c r="A256" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B256" s="9" t="n">
+      <c r="B256" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C256" s="10" t="inlineStr">
+      <c r="C256" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D256" s="10" t="inlineStr">
+      <c r="D256" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E256" s="11" t="n">
+      <c r="E256" s="10" t="n">
         <v>1214794.5</v>
       </c>
-      <c r="F256" s="8" t="n">
+      <c r="F256" s="11" t="n">
         <v>186</v>
       </c>
-      <c r="G256" s="8" t="n">
+      <c r="G256" s="11" t="n">
         <v>186</v>
       </c>
       <c r="H256" s="12" t="n">
@@ -8528,26 +8528,26 @@
       <c r="A257" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B257" s="14" t="n">
+      <c r="B257" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C257" s="15" t="inlineStr">
+      <c r="C257" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D257" s="15" t="inlineStr">
+      <c r="D257" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E257" s="16" t="n">
+      <c r="E257" s="15" t="n">
         <v>98468486.06</v>
       </c>
-      <c r="F257" s="13" t="n">
+      <c r="F257" s="16" t="n">
         <v>10315</v>
       </c>
-      <c r="G257" s="13" t="n">
+      <c r="G257" s="16" t="n">
         <v>9436</v>
       </c>
       <c r="H257" s="17" t="n">
@@ -8558,26 +8558,26 @@
       <c r="A258" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B258" s="9" t="n">
+      <c r="B258" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C258" s="10" t="inlineStr">
+      <c r="C258" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D258" s="10" t="inlineStr">
+      <c r="D258" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E258" s="11" t="n">
+      <c r="E258" s="10" t="n">
         <v>8915797.779999999</v>
       </c>
-      <c r="F258" s="8" t="n">
+      <c r="F258" s="11" t="n">
         <v>607</v>
       </c>
-      <c r="G258" s="8" t="n">
+      <c r="G258" s="11" t="n">
         <v>525</v>
       </c>
       <c r="H258" s="12" t="n">
@@ -8588,26 +8588,26 @@
       <c r="A259" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B259" s="14" t="n">
+      <c r="B259" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C259" s="15" t="inlineStr">
+      <c r="C259" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D259" s="15" t="inlineStr">
+      <c r="D259" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E259" s="16" t="n">
+      <c r="E259" s="15" t="n">
         <v>6213484.65</v>
       </c>
-      <c r="F259" s="13" t="n">
+      <c r="F259" s="16" t="n">
         <v>3349</v>
       </c>
-      <c r="G259" s="13" t="n">
+      <c r="G259" s="16" t="n">
         <v>3313</v>
       </c>
       <c r="H259" s="17" t="n">
@@ -8618,26 +8618,26 @@
       <c r="A260" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B260" s="9" t="n">
+      <c r="B260" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C260" s="10" t="inlineStr">
+      <c r="C260" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D260" s="10" t="inlineStr">
+      <c r="D260" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E260" s="11" t="n">
+      <c r="E260" s="10" t="n">
         <v>3226745.55</v>
       </c>
-      <c r="F260" s="8" t="n">
+      <c r="F260" s="11" t="n">
         <v>219</v>
       </c>
-      <c r="G260" s="8" t="n">
+      <c r="G260" s="11" t="n">
         <v>202</v>
       </c>
       <c r="H260" s="12" t="n">
@@ -8648,26 +8648,26 @@
       <c r="A261" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B261" s="14" t="n">
+      <c r="B261" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C261" s="15" t="inlineStr">
+      <c r="C261" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D261" s="15" t="inlineStr">
+      <c r="D261" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E261" s="16" t="n">
+      <c r="E261" s="15" t="n">
         <v>1114212.4</v>
       </c>
-      <c r="F261" s="13" t="n">
+      <c r="F261" s="16" t="n">
         <v>184</v>
       </c>
-      <c r="G261" s="13" t="n">
+      <c r="G261" s="16" t="n">
         <v>184</v>
       </c>
       <c r="H261" s="17" t="n">
@@ -8678,26 +8678,26 @@
       <c r="A262" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B262" s="9" t="n">
+      <c r="B262" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C262" s="10" t="inlineStr">
+      <c r="C262" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D262" s="10" t="inlineStr">
+      <c r="D262" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E262" s="11" t="n">
+      <c r="E262" s="10" t="n">
         <v>99890777.22</v>
       </c>
-      <c r="F262" s="8" t="n">
+      <c r="F262" s="11" t="n">
         <v>10483</v>
       </c>
-      <c r="G262" s="8" t="n">
+      <c r="G262" s="11" t="n">
         <v>9531</v>
       </c>
       <c r="H262" s="12" t="n">
@@ -8708,26 +8708,26 @@
       <c r="A263" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B263" s="14" t="n">
+      <c r="B263" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C263" s="15" t="inlineStr">
+      <c r="C263" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D263" s="15" t="inlineStr">
+      <c r="D263" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E263" s="16" t="n">
+      <c r="E263" s="15" t="n">
         <v>9948062.43</v>
       </c>
-      <c r="F263" s="13" t="n">
+      <c r="F263" s="16" t="n">
         <v>627</v>
       </c>
-      <c r="G263" s="13" t="n">
+      <c r="G263" s="16" t="n">
         <v>553</v>
       </c>
       <c r="H263" s="17" t="n">
@@ -8738,26 +8738,26 @@
       <c r="A264" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B264" s="9" t="n">
+      <c r="B264" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C264" s="10" t="inlineStr">
+      <c r="C264" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D264" s="10" t="inlineStr">
+      <c r="D264" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E264" s="11" t="n">
+      <c r="E264" s="10" t="n">
         <v>5935012.12</v>
       </c>
-      <c r="F264" s="8" t="n">
+      <c r="F264" s="11" t="n">
         <v>3197</v>
       </c>
-      <c r="G264" s="8" t="n">
+      <c r="G264" s="11" t="n">
         <v>3122</v>
       </c>
       <c r="H264" s="12" t="n">
@@ -8768,26 +8768,26 @@
       <c r="A265" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B265" s="14" t="n">
+      <c r="B265" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C265" s="15" t="inlineStr">
+      <c r="C265" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D265" s="15" t="inlineStr">
+      <c r="D265" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E265" s="16" t="n">
+      <c r="E265" s="15" t="n">
         <v>3170130.98</v>
       </c>
-      <c r="F265" s="13" t="n">
+      <c r="F265" s="16" t="n">
         <v>193</v>
       </c>
-      <c r="G265" s="13" t="n">
+      <c r="G265" s="16" t="n">
         <v>178</v>
       </c>
       <c r="H265" s="17" t="n">
@@ -8798,26 +8798,26 @@
       <c r="A266" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B266" s="9" t="n">
+      <c r="B266" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C266" s="10" t="inlineStr">
+      <c r="C266" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D266" s="10" t="inlineStr">
+      <c r="D266" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E266" s="11" t="n">
+      <c r="E266" s="10" t="n">
         <v>1125434.68</v>
       </c>
-      <c r="F266" s="8" t="n">
+      <c r="F266" s="11" t="n">
         <v>184</v>
       </c>
-      <c r="G266" s="8" t="n">
+      <c r="G266" s="11" t="n">
         <v>184</v>
       </c>
       <c r="H266" s="12" t="n">
@@ -8828,26 +8828,26 @@
       <c r="A267" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B267" s="14" t="n">
+      <c r="B267" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C267" s="15" t="inlineStr">
+      <c r="C267" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D267" s="15" t="inlineStr">
+      <c r="D267" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E267" s="16" t="n">
+      <c r="E267" s="15" t="n">
         <v>103044691.26</v>
       </c>
-      <c r="F267" s="13" t="n">
+      <c r="F267" s="16" t="n">
         <v>10495</v>
       </c>
-      <c r="G267" s="13" t="n">
+      <c r="G267" s="16" t="n">
         <v>9697</v>
       </c>
       <c r="H267" s="17" t="n">
@@ -8858,26 +8858,26 @@
       <c r="A268" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B268" s="9" t="n">
+      <c r="B268" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C268" s="10" t="inlineStr">
+      <c r="C268" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D268" s="10" t="inlineStr">
+      <c r="D268" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E268" s="11" t="n">
+      <c r="E268" s="10" t="n">
         <v>9735634.220000001</v>
       </c>
-      <c r="F268" s="8" t="n">
+      <c r="F268" s="11" t="n">
         <v>634</v>
       </c>
-      <c r="G268" s="8" t="n">
+      <c r="G268" s="11" t="n">
         <v>558</v>
       </c>
       <c r="H268" s="12" t="n">
@@ -8888,26 +8888,26 @@
       <c r="A269" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B269" s="14" t="n">
+      <c r="B269" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C269" s="15" t="inlineStr">
+      <c r="C269" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D269" s="15" t="inlineStr">
+      <c r="D269" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E269" s="16" t="n">
+      <c r="E269" s="15" t="n">
         <v>6403902.52</v>
       </c>
-      <c r="F269" s="13" t="n">
+      <c r="F269" s="16" t="n">
         <v>3265</v>
       </c>
-      <c r="G269" s="13" t="n">
+      <c r="G269" s="16" t="n">
         <v>3237</v>
       </c>
       <c r="H269" s="17" t="n">
@@ -8918,26 +8918,26 @@
       <c r="A270" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B270" s="9" t="n">
+      <c r="B270" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C270" s="10" t="inlineStr">
+      <c r="C270" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D270" s="10" t="inlineStr">
+      <c r="D270" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E270" s="11" t="n">
+      <c r="E270" s="10" t="n">
         <v>3079201.26</v>
       </c>
-      <c r="F270" s="8" t="n">
+      <c r="F270" s="11" t="n">
         <v>184</v>
       </c>
-      <c r="G270" s="8" t="n">
+      <c r="G270" s="11" t="n">
         <v>176</v>
       </c>
       <c r="H270" s="12" t="n">
@@ -8948,26 +8948,26 @@
       <c r="A271" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B271" s="14" t="n">
+      <c r="B271" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C271" s="15" t="inlineStr">
+      <c r="C271" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D271" s="15" t="inlineStr">
+      <c r="D271" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E271" s="16" t="n">
+      <c r="E271" s="15" t="n">
         <v>1120747.43</v>
       </c>
-      <c r="F271" s="13" t="n">
+      <c r="F271" s="16" t="n">
         <v>183</v>
       </c>
-      <c r="G271" s="13" t="n">
+      <c r="G271" s="16" t="n">
         <v>183</v>
       </c>
       <c r="H271" s="17" t="n">
@@ -8978,26 +8978,26 @@
       <c r="A272" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B272" s="9" t="n">
+      <c r="B272" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C272" s="10" t="inlineStr">
+      <c r="C272" s="9" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D272" s="10" t="inlineStr">
+      <c r="D272" s="9" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E272" s="11" t="n">
+      <c r="E272" s="10" t="n">
         <v>118069916.96</v>
       </c>
-      <c r="F272" s="8" t="n">
+      <c r="F272" s="11" t="n">
         <v>14968</v>
       </c>
-      <c r="G272" s="8" t="n">
+      <c r="G272" s="11" t="n">
         <v>9742</v>
       </c>
       <c r="H272" s="12" t="n">
@@ -9008,26 +9008,26 @@
       <c r="A273" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B273" s="14" t="n">
+      <c r="B273" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C273" s="15" t="inlineStr">
+      <c r="C273" s="14" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D273" s="15" t="inlineStr">
+      <c r="D273" s="14" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E273" s="16" t="n">
+      <c r="E273" s="15" t="n">
         <v>9735182.08</v>
       </c>
-      <c r="F273" s="13" t="n">
+      <c r="F273" s="16" t="n">
         <v>742</v>
       </c>
-      <c r="G273" s="13" t="n">
+      <c r="G273" s="16" t="n">
         <v>550</v>
       </c>
       <c r="H273" s="17" t="n">
@@ -9038,26 +9038,26 @@
       <c r="A274" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B274" s="9" t="n">
+      <c r="B274" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C274" s="10" t="inlineStr">
+      <c r="C274" s="9" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D274" s="10" t="inlineStr">
+      <c r="D274" s="9" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E274" s="11" t="n">
+      <c r="E274" s="10" t="n">
         <v>6328962</v>
       </c>
-      <c r="F274" s="8" t="n">
+      <c r="F274" s="11" t="n">
         <v>3268</v>
       </c>
-      <c r="G274" s="8" t="n">
+      <c r="G274" s="11" t="n">
         <v>3242</v>
       </c>
       <c r="H274" s="12" t="n">
@@ -9068,26 +9068,26 @@
       <c r="A275" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B275" s="14" t="n">
+      <c r="B275" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C275" s="15" t="inlineStr">
+      <c r="C275" s="14" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D275" s="15" t="inlineStr">
+      <c r="D275" s="14" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E275" s="16" t="n">
+      <c r="E275" s="15" t="n">
         <v>3647493.07</v>
       </c>
-      <c r="F275" s="13" t="n">
+      <c r="F275" s="16" t="n">
         <v>206</v>
       </c>
-      <c r="G275" s="13" t="n">
+      <c r="G275" s="16" t="n">
         <v>184</v>
       </c>
       <c r="H275" s="17" t="n">
@@ -9098,26 +9098,26 @@
       <c r="A276" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B276" s="9" t="n">
+      <c r="B276" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C276" s="10" t="inlineStr">
+      <c r="C276" s="9" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D276" s="10" t="inlineStr">
+      <c r="D276" s="9" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E276" s="11" t="n">
+      <c r="E276" s="10" t="n">
         <v>1104776.27</v>
       </c>
-      <c r="F276" s="8" t="n">
+      <c r="F276" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="G276" s="8" t="n">
+      <c r="G276" s="11" t="n">
         <v>180</v>
       </c>
       <c r="H276" s="12" t="n">
@@ -9128,26 +9128,26 @@
       <c r="A277" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B277" s="14" t="n">
+      <c r="B277" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C277" s="15" t="inlineStr">
+      <c r="C277" s="14" t="inlineStr">
         <is>
           <t>Efetivos e empregados publicos (carreira)</t>
         </is>
       </c>
-      <c r="D277" s="15" t="inlineStr">
+      <c r="D277" s="14" t="inlineStr">
         <is>
           <t>efetivos</t>
         </is>
       </c>
-      <c r="E277" s="16" t="n">
+      <c r="E277" s="15" t="n">
         <v>106596223.55</v>
       </c>
-      <c r="F277" s="13" t="n">
+      <c r="F277" s="16" t="n">
         <v>10763</v>
       </c>
-      <c r="G277" s="13" t="n">
+      <c r="G277" s="16" t="n">
         <v>10105</v>
       </c>
       <c r="H277" s="17" t="n">
@@ -9158,26 +9158,26 @@
       <c r="A278" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B278" s="9" t="n">
+      <c r="B278" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C278" s="10" t="inlineStr">
+      <c r="C278" s="9" t="inlineStr">
         <is>
           <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D278" s="10" t="inlineStr">
+      <c r="D278" s="9" t="inlineStr">
         <is>
           <t>funcao_confianca</t>
         </is>
       </c>
-      <c r="E278" s="11" t="n">
+      <c r="E278" s="10" t="n">
         <v>9757394.470000001</v>
       </c>
-      <c r="F278" s="8" t="n">
+      <c r="F278" s="11" t="n">
         <v>639</v>
       </c>
-      <c r="G278" s="8" t="n">
+      <c r="G278" s="11" t="n">
         <v>563</v>
       </c>
       <c r="H278" s="12" t="n">
@@ -9188,26 +9188,26 @@
       <c r="A279" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B279" s="14" t="n">
+      <c r="B279" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C279" s="15" t="inlineStr">
+      <c r="C279" s="14" t="inlineStr">
         <is>
           <t>Temporarios, estagiarios e eventuais</t>
         </is>
       </c>
-      <c r="D279" s="15" t="inlineStr">
+      <c r="D279" s="14" t="inlineStr">
         <is>
           <t>flexiveis</t>
         </is>
       </c>
-      <c r="E279" s="16" t="n">
+      <c r="E279" s="15" t="n">
         <v>4003173.29</v>
       </c>
-      <c r="F279" s="13" t="n">
+      <c r="F279" s="16" t="n">
         <v>2911</v>
       </c>
-      <c r="G279" s="13" t="n">
+      <c r="G279" s="16" t="n">
         <v>2885</v>
       </c>
       <c r="H279" s="17" t="n">
@@ -9218,26 +9218,26 @@
       <c r="A280" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B280" s="9" t="n">
+      <c r="B280" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C280" s="10" t="inlineStr">
+      <c r="C280" s="9" t="inlineStr">
         <is>
           <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
         </is>
       </c>
-      <c r="D280" s="10" t="inlineStr">
+      <c r="D280" s="9" t="inlineStr">
         <is>
           <t>comissionados</t>
         </is>
       </c>
-      <c r="E280" s="11" t="n">
+      <c r="E280" s="10" t="n">
         <v>3329784.06</v>
       </c>
-      <c r="F280" s="8" t="n">
+      <c r="F280" s="11" t="n">
         <v>193</v>
       </c>
-      <c r="G280" s="8" t="n">
+      <c r="G280" s="11" t="n">
         <v>184</v>
       </c>
       <c r="H280" s="12" t="n">
@@ -9248,34 +9248,184 @@
       <c r="A281" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="B281" s="14" t="n">
+      <c r="B281" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C281" s="15" t="inlineStr">
+      <c r="C281" s="14" t="inlineStr">
         <is>
           <t>Inativos e pensionistas</t>
         </is>
       </c>
-      <c r="D281" s="15" t="inlineStr">
+      <c r="D281" s="14" t="inlineStr">
         <is>
           <t>inativos</t>
         </is>
       </c>
-      <c r="E281" s="16" t="n">
+      <c r="E281" s="15" t="n">
         <v>1097987.4</v>
       </c>
-      <c r="F281" s="13" t="n">
+      <c r="F281" s="16" t="n">
         <v>179</v>
       </c>
-      <c r="G281" s="13" t="n">
+      <c r="G281" s="16" t="n">
         <v>179</v>
       </c>
       <c r="H281" s="17" t="n">
         <v>0.88</v>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B282" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C282" s="9" t="inlineStr">
+        <is>
+          <t>Efetivos e empregados publicos (carreira)</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>efetivos</t>
+        </is>
+      </c>
+      <c r="E282" s="10" t="n">
+        <v>109147551.35</v>
+      </c>
+      <c r="F282" s="11" t="n">
+        <v>10882</v>
+      </c>
+      <c r="G282" s="11" t="n">
+        <v>10202</v>
+      </c>
+      <c r="H282" s="12" t="n">
+        <v>83.98</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B283" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C283" s="14" t="inlineStr">
+        <is>
+          <t>Efetivos em funcao de confianca (sobre vinculo de carreira)</t>
+        </is>
+      </c>
+      <c r="D283" s="14" t="inlineStr">
+        <is>
+          <t>funcao_confianca</t>
+        </is>
+      </c>
+      <c r="E283" s="15" t="n">
+        <v>9911529.310000001</v>
+      </c>
+      <c r="F283" s="16" t="n">
+        <v>640</v>
+      </c>
+      <c r="G283" s="16" t="n">
+        <v>564</v>
+      </c>
+      <c r="H283" s="17" t="n">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B284" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C284" s="9" t="inlineStr">
+        <is>
+          <t>Temporarios, estagiarios e eventuais</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>flexiveis</t>
+        </is>
+      </c>
+      <c r="E284" s="10" t="n">
+        <v>6702137.88</v>
+      </c>
+      <c r="F284" s="11" t="n">
+        <v>3356</v>
+      </c>
+      <c r="G284" s="11" t="n">
+        <v>3353</v>
+      </c>
+      <c r="H284" s="12" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B285" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C285" s="14" t="inlineStr">
+        <is>
+          <t>Comissionados e agentes politicos (sem vinculo de carreira)</t>
+        </is>
+      </c>
+      <c r="D285" s="14" t="inlineStr">
+        <is>
+          <t>comissionados</t>
+        </is>
+      </c>
+      <c r="E285" s="15" t="n">
+        <v>3136223.22</v>
+      </c>
+      <c r="F285" s="16" t="n">
+        <v>201</v>
+      </c>
+      <c r="G285" s="16" t="n">
+        <v>174</v>
+      </c>
+      <c r="H285" s="17" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B286" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C286" s="9" t="inlineStr">
+        <is>
+          <t>Inativos e pensionistas</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>inativos</t>
+        </is>
+      </c>
+      <c r="E286" s="10" t="n">
+        <v>1073778.06</v>
+      </c>
+      <c r="F286" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="G286" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="H286" s="12" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H281"/>
+  <autoFilter ref="A1:H286"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>